--- a/tame_output/ON/bt/strategyON_20240726.xlsx
+++ b/tame_output/ON/bt/strategyON_20240726.xlsx
@@ -48379,10 +48379,10 @@
         <v>3.806803414596859</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.013512071007104</v>
+        <v>-4.01366240418647</v>
       </c>
       <c r="E2036" t="n">
-        <v>2.201042161880271</v>
+        <v>2.200982028608524</v>
       </c>
       <c r="F2036" t="n">
         <v>0.4942707713298854</v>

--- a/tame_output/ON/bt/strategyON_20240726.xlsx
+++ b/tame_output/ON/bt/strategyON_20240726.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-76.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.4%</t>
+          <t>111.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.1%</t>
+          <t>125.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.4%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.1%</t>
+          <t>-48.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.1%</t>
+          <t>-71.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.4%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>455.7%</t>
+          <t>455.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-562.9%</t>
+          <t>-578.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.2%</t>
+          <t>-34.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-156.1%</t>
+          <t>-162.2%</t>
         </is>
       </c>
     </row>
@@ -48379,10 +48379,10 @@
         <v>3.806803414596859</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.01366240418647</v>
+        <v>-4.165445578392699</v>
       </c>
       <c r="E2036" t="n">
-        <v>2.200982028608524</v>
+        <v>2.140268758926033</v>
       </c>
       <c r="F2036" t="n">
         <v>0.4942707713298854</v>

--- a/tame_output/ON/bt/strategyON_20240726.xlsx
+++ b/tame_output/ON/bt/strategyON_20240726.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>51.0%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>83.7%</t>
+          <t>83.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>68.9%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.2%</t>
+          <t>-76.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.3%</t>
+          <t>111.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.0%</t>
+          <t>125.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.9%</t>
+          <t>-72.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>455.3%</t>
+          <t>456.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-7.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-578.1%</t>
+          <t>-581.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-162.2%</t>
+          <t>-163.6%</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>79.1%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-20.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-35.7%</t>
+          <t>-66.2%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2036"/>
+  <dimension ref="A1:G2037"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47804,10 +47804,10 @@
         <v>3.533162878843719</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.16624226150958</v>
+        <v>-3.201739407669643</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.266309549926139</v>
+        <v>2.252110691462114</v>
       </c>
       <c r="F2011" t="n">
         <v>0.623874409742177</v>
@@ -47827,10 +47827,10 @@
         <v>3.533162878843719</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.16780390432444</v>
+        <v>-3.203301050484503</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.265684892800195</v>
+        <v>2.25148603433617</v>
       </c>
       <c r="F2012" t="n">
         <v>0.623874409742177</v>
@@ -47850,10 +47850,10 @@
         <v>3.531686919970721</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.195704691433913</v>
+        <v>-3.231201837593976</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.253048619083408</v>
+        <v>2.238849760619383</v>
       </c>
       <c r="F2013" t="n">
         <v>0.5892774855992422</v>
@@ -47873,10 +47873,10 @@
         <v>3.528451363947919</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.318230794136807</v>
+        <v>-3.353727940296869</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.200802621979449</v>
+        <v>2.186603763515424</v>
       </c>
       <c r="F2014" t="n">
         <v>0.4667513828963483</v>
@@ -47896,10 +47896,10 @@
         <v>3.595157323538423</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.338292115413314</v>
+        <v>-3.373789261573376</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.25948405305935</v>
+        <v>2.245285194595326</v>
       </c>
       <c r="F2015" t="n">
         <v>0.4466900616198413</v>
@@ -47919,10 +47919,10 @@
         <v>3.73546904254027</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.595012933408138</v>
+        <v>-3.6305100795682</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.297107444863268</v>
+        <v>2.282908586399243</v>
       </c>
       <c r="F2016" t="n">
         <v>0.3382754874760265</v>
@@ -47942,10 +47942,10 @@
         <v>3.80444931168591</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.748999351184279</v>
+        <v>-3.784496497344341</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.304493146898452</v>
+        <v>2.290294288434426</v>
       </c>
       <c r="F2017" t="n">
         <v>0.3382754874760265</v>
@@ -47965,10 +47965,10 @@
         <v>3.790500513806031</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.698477447356613</v>
+        <v>-3.733974593516675</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.310753110549638</v>
+        <v>2.296554252085614</v>
       </c>
       <c r="F2018" t="n">
         <v>0.3382754874760265</v>
@@ -47988,10 +47988,10 @@
         <v>3.802371002861445</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.950952601364337</v>
+        <v>-3.986449747524399</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.221633538001963</v>
+        <v>2.207434679537938</v>
       </c>
       <c r="F2019" t="n">
         <v>0.3382754874760265</v>
@@ -48011,10 +48011,10 @@
         <v>3.803581537380389</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.220425403286045</v>
+        <v>-4.255922549446107</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.115054951752223</v>
+        <v>2.100856093288198</v>
       </c>
       <c r="F2020" t="n">
         <v>0.3382754874760265</v>
@@ -48034,10 +48034,10 @@
         <v>3.80770327960771</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.377969475015487</v>
+        <v>-4.413466621175549</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.056159065287768</v>
+        <v>2.041960206823743</v>
       </c>
       <c r="F2021" t="n">
         <v>0.271373682335752</v>
@@ -48057,10 +48057,10 @@
         <v>3.802781132343899</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.65593387059876</v>
+        <v>-4.691431016758822</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.940051159790648</v>
+        <v>1.925852301326623</v>
       </c>
       <c r="F2022" t="n">
         <v>0.1817539480502677</v>
@@ -48080,10 +48080,10 @@
         <v>3.964985189042944</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.772901563237651</v>
+        <v>-4.808398709397713</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.055468139434136</v>
+        <v>2.041269280970111</v>
       </c>
       <c r="F2023" t="n">
         <v>0.1817539480502677</v>
@@ -48103,10 +48103,10 @@
         <v>3.959831827006758</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.857619505458604</v>
+        <v>-4.893116651618667</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.016427600509568</v>
+        <v>2.002228742045544</v>
       </c>
       <c r="F2024" t="n">
         <v>0.09663791912222136</v>
@@ -48126,10 +48126,10 @@
         <v>3.970061244575249</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.939554323727488</v>
+        <v>-4.97505146988755</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.993883090770507</v>
+        <v>1.979684232306482</v>
       </c>
       <c r="F2025" t="n">
         <v>0.08670317353514118</v>
@@ -48149,10 +48149,10 @@
         <v>3.978986883031151</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.885816150327225</v>
+        <v>-4.921313296487288</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.024303998586514</v>
+        <v>2.010105140122489</v>
       </c>
       <c r="F2026" t="n">
         <v>0.1404413469354033</v>
@@ -48172,10 +48172,10 @@
         <v>3.971139770275327</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.775809866850004</v>
+        <v>-4.811307013010066</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.060459399221578</v>
+        <v>2.046260540757554</v>
       </c>
       <c r="F2027" t="n">
         <v>0.1636459188526785</v>
@@ -48195,10 +48195,10 @@
         <v>3.975389780997301</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.632750291109078</v>
+        <v>-4.668247437269141</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.121933240239923</v>
+        <v>2.107734381775898</v>
       </c>
       <c r="F2028" t="n">
         <v>0.1716593454426578</v>
@@ -48218,10 +48218,10 @@
         <v>3.982650663879838</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.33130356563724</v>
+        <v>-4.366800711797303</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.249772813311194</v>
+        <v>2.235573954847169</v>
       </c>
       <c r="F2029" t="n">
         <v>0.473106070914495</v>
@@ -48241,10 +48241,10 @@
         <v>3.983621841632548</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.38625876208031</v>
+        <v>-4.421755908240373</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.228761912486677</v>
+        <v>2.214563054022651</v>
       </c>
       <c r="F2030" t="n">
         <v>0.473106070914495</v>
@@ -48264,10 +48264,10 @@
         <v>3.984464746012303</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.335220386073789</v>
+        <v>-4.370717532233853</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.250020167269041</v>
+        <v>2.235821308805015</v>
       </c>
       <c r="F2031" t="n">
         <v>0.473106070914495</v>
@@ -48287,10 +48287,10 @@
         <v>4.003502844886449</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.294081091207159</v>
+        <v>-4.329578237367222</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.285513984089838</v>
+        <v>2.271315125625813</v>
       </c>
       <c r="F2032" t="n">
         <v>0.5142453657811259</v>
@@ -48310,10 +48310,10 @@
         <v>3.819686841010383</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.183474951127557</v>
+        <v>-4.21897209728762</v>
       </c>
       <c r="E2033" t="n">
-        <v>2.145940436245613</v>
+        <v>2.131741577781588</v>
       </c>
       <c r="F2033" t="n">
         <v>0.6248515058607279</v>
@@ -48333,10 +48333,10 @@
         <v>3.823188885084347</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.314055685658399</v>
+        <v>-4.349552831818462</v>
       </c>
       <c r="E2034" t="n">
-        <v>2.09721018650724</v>
+        <v>2.083011328043215</v>
       </c>
       <c r="F2034" t="n">
         <v>0.4942707713298854</v>
@@ -48356,10 +48356,10 @@
         <v>3.80761570416043</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.149559351467437</v>
+        <v>-4.1850564976275</v>
       </c>
       <c r="E2035" t="n">
-        <v>2.147435539259708</v>
+        <v>2.133236680795682</v>
       </c>
       <c r="F2035" t="n">
         <v>0.4942707713298854</v>
@@ -48373,22 +48373,45 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.726568587429755</v>
+        <v>3.821044820462767</v>
       </c>
       <c r="C2036" t="n">
         <v>3.806803414596859</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.165445578392699</v>
+        <v>-4.200942724552762</v>
       </c>
       <c r="E2036" t="n">
-        <v>2.140268758926033</v>
+        <v>2.126069900462007</v>
       </c>
       <c r="F2036" t="n">
         <v>0.4942707713298854</v>
       </c>
       <c r="G2036" t="n">
         <v>4.103365877394791</v>
+      </c>
+    </row>
+    <row r="2037">
+      <c r="A2037" s="2" t="n">
+        <v>45499</v>
+      </c>
+      <c r="B2037" t="n">
+        <v>3.791242606924984</v>
+      </c>
+      <c r="C2037" t="n">
+        <v>3.805267014986832</v>
+      </c>
+      <c r="D2037" t="n">
+        <v>-4.200942724552762</v>
+      </c>
+      <c r="E2037" t="n">
+        <v>2.126069900462007</v>
+      </c>
+      <c r="F2037" t="n">
+        <v>0.4942707713298854</v>
+      </c>
+      <c r="G2037" t="n">
+        <v>3.7983308119732</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240726.xlsx
+++ b/tame_output/ON/bt/strategyON_20240726.xlsx
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.3%</t>
+          <t>-75.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.4%</t>
+          <t>111.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.7%</t>
+          <t>-48.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.0%</t>
+          <t>-71.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>92.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>456.1%</t>
+          <t>456.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-581.7%</t>
+          <t>-566.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.6%</t>
+          <t>-34.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-163.6%</t>
+          <t>-157.7%</t>
         </is>
       </c>
     </row>
@@ -47804,10 +47804,10 @@
         <v>3.533162878843719</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.201739407669643</v>
+        <v>-3.193459850951299</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.252110691462114</v>
+        <v>2.255422514149451</v>
       </c>
       <c r="F2011" t="n">
         <v>0.623874409742177</v>
@@ -47827,10 +47827,10 @@
         <v>3.533162878843719</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.203301050484503</v>
+        <v>-3.195021493766159</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.25148603433617</v>
+        <v>2.254797857023508</v>
       </c>
       <c r="F2012" t="n">
         <v>0.623874409742177</v>
@@ -47850,10 +47850,10 @@
         <v>3.531686919970721</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.231201837593976</v>
+        <v>-3.222922280875632</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.238849760619383</v>
+        <v>2.242161583306721</v>
       </c>
       <c r="F2013" t="n">
         <v>0.5892774855992422</v>
@@ -47873,10 +47873,10 @@
         <v>3.528451363947919</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.353727940296869</v>
+        <v>-3.345448383578526</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.186603763515424</v>
+        <v>2.189915586202762</v>
       </c>
       <c r="F2014" t="n">
         <v>0.4667513828963483</v>
@@ -47896,10 +47896,10 @@
         <v>3.595157323538423</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.373789261573376</v>
+        <v>-3.365509704855033</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.245285194595326</v>
+        <v>2.248597017282663</v>
       </c>
       <c r="F2015" t="n">
         <v>0.4466900616198413</v>
@@ -47919,10 +47919,10 @@
         <v>3.73546904254027</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.6305100795682</v>
+        <v>-3.622230522849857</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.282908586399243</v>
+        <v>2.28622040908658</v>
       </c>
       <c r="F2016" t="n">
         <v>0.3382754874760265</v>
@@ -47942,10 +47942,10 @@
         <v>3.80444931168591</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.784496497344341</v>
+        <v>-3.776216940625997</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.290294288434426</v>
+        <v>2.293606111121764</v>
       </c>
       <c r="F2017" t="n">
         <v>0.3382754874760265</v>
@@ -47965,10 +47965,10 @@
         <v>3.790500513806031</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.733974593516675</v>
+        <v>-3.725695036798331</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.296554252085614</v>
+        <v>2.299866074772951</v>
       </c>
       <c r="F2018" t="n">
         <v>0.3382754874760265</v>
@@ -47988,10 +47988,10 @@
         <v>3.802371002861445</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.986449747524399</v>
+        <v>-3.978170190806056</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.207434679537938</v>
+        <v>2.210746502225275</v>
       </c>
       <c r="F2019" t="n">
         <v>0.3382754874760265</v>
@@ -48011,10 +48011,10 @@
         <v>3.803581537380389</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.255922549446107</v>
+        <v>-4.247642992727764</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.100856093288198</v>
+        <v>2.104167915975536</v>
       </c>
       <c r="F2020" t="n">
         <v>0.3382754874760265</v>
@@ -48034,10 +48034,10 @@
         <v>3.80770327960771</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.413466621175549</v>
+        <v>-4.405187064457206</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.041960206823743</v>
+        <v>2.04527202951108</v>
       </c>
       <c r="F2021" t="n">
         <v>0.271373682335752</v>
@@ -48057,10 +48057,10 @@
         <v>3.802781132343899</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.691431016758822</v>
+        <v>-4.683151460040479</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.925852301326623</v>
+        <v>1.929164124013961</v>
       </c>
       <c r="F2022" t="n">
         <v>0.1817539480502677</v>
@@ -48080,10 +48080,10 @@
         <v>3.964985189042944</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.808398709397713</v>
+        <v>-4.80011915267937</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.041269280970111</v>
+        <v>2.044581103657448</v>
       </c>
       <c r="F2023" t="n">
         <v>0.1817539480502677</v>
@@ -48103,10 +48103,10 @@
         <v>3.959831827006758</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.893116651618667</v>
+        <v>-4.884837094900323</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.002228742045544</v>
+        <v>2.005540564732881</v>
       </c>
       <c r="F2024" t="n">
         <v>0.09663791912222136</v>
@@ -48126,10 +48126,10 @@
         <v>3.970061244575249</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.97505146988755</v>
+        <v>-4.966771913169207</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.979684232306482</v>
+        <v>1.982996054993819</v>
       </c>
       <c r="F2025" t="n">
         <v>0.08670317353514118</v>
@@ -48149,10 +48149,10 @@
         <v>3.978986883031151</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.921313296487288</v>
+        <v>-4.913033739768944</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.010105140122489</v>
+        <v>2.013416962809826</v>
       </c>
       <c r="F2026" t="n">
         <v>0.1404413469354033</v>
@@ -48172,10 +48172,10 @@
         <v>3.971139770275327</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.811307013010066</v>
+        <v>-4.803027456291723</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.046260540757554</v>
+        <v>2.049572363444891</v>
       </c>
       <c r="F2027" t="n">
         <v>0.1636459188526785</v>
@@ -48195,10 +48195,10 @@
         <v>3.975389780997301</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.668247437269141</v>
+        <v>-4.659967880550797</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.107734381775898</v>
+        <v>2.111046204463236</v>
       </c>
       <c r="F2028" t="n">
         <v>0.1716593454426578</v>
@@ -48218,10 +48218,10 @@
         <v>3.982650663879838</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.366800711797303</v>
+        <v>-4.358521155078959</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.235573954847169</v>
+        <v>2.238885777534507</v>
       </c>
       <c r="F2029" t="n">
         <v>0.473106070914495</v>
@@ -48241,10 +48241,10 @@
         <v>3.983621841632548</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.421755908240373</v>
+        <v>-4.413476351522029</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.214563054022651</v>
+        <v>2.217874876709989</v>
       </c>
       <c r="F2030" t="n">
         <v>0.473106070914495</v>
@@ -48264,10 +48264,10 @@
         <v>3.984464746012303</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.370717532233853</v>
+        <v>-4.362437975515508</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.235821308805015</v>
+        <v>2.239133131492353</v>
       </c>
       <c r="F2031" t="n">
         <v>0.473106070914495</v>
@@ -48287,10 +48287,10 @@
         <v>4.003502844886449</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.329578237367222</v>
+        <v>-4.321298680648877</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.271315125625813</v>
+        <v>2.274626948313151</v>
       </c>
       <c r="F2032" t="n">
         <v>0.5142453657811259</v>
@@ -48310,10 +48310,10 @@
         <v>3.819686841010383</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.21897209728762</v>
+        <v>-4.210692540569275</v>
       </c>
       <c r="E2033" t="n">
-        <v>2.131741577781588</v>
+        <v>2.135053400468926</v>
       </c>
       <c r="F2033" t="n">
         <v>0.6248515058607279</v>
@@ -48333,10 +48333,10 @@
         <v>3.823188885084347</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.349552831818462</v>
+        <v>-4.341273275100118</v>
       </c>
       <c r="E2034" t="n">
-        <v>2.083011328043215</v>
+        <v>2.086323150730553</v>
       </c>
       <c r="F2034" t="n">
         <v>0.4942707713298854</v>
@@ -48356,10 +48356,10 @@
         <v>3.80761570416043</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.1850564976275</v>
+        <v>-4.176776940909156</v>
       </c>
       <c r="E2035" t="n">
-        <v>2.133236680795682</v>
+        <v>2.13654850348302</v>
       </c>
       <c r="F2035" t="n">
         <v>0.4942707713298854</v>
@@ -48379,10 +48379,10 @@
         <v>3.806803414596859</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.200942724552762</v>
+        <v>-4.052296460185205</v>
       </c>
       <c r="E2036" t="n">
-        <v>2.126069900462007</v>
+        <v>2.185528406209031</v>
       </c>
       <c r="F2036" t="n">
         <v>0.4942707713298854</v>
@@ -48402,10 +48402,10 @@
         <v>3.805267014986832</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.200942724552762</v>
+        <v>-4.052296460185205</v>
       </c>
       <c r="E2037" t="n">
-        <v>2.126069900462007</v>
+        <v>2.185528406209031</v>
       </c>
       <c r="F2037" t="n">
         <v>0.4942707713298854</v>

--- a/tame_output/ON/bt/strategyON_20240726.xlsx
+++ b/tame_output/ON/bt/strategyON_20240726.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>54.3%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>83.6%</t>
+          <t>83.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>69.1%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.7%</t>
+          <t>-76.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.5%</t>
+          <t>111.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.3%</t>
+          <t>97.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.1%</t>
+          <t>-48.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.3%</t>
+          <t>-71.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.4%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.9%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-566.8%</t>
+          <t>-575.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.2%</t>
+          <t>-34.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-47.5%</t>
+          <t>-47.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-157.7%</t>
+          <t>-161.2%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,16 +1242,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.3%</t>
+          <t>-25.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-9.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-104.6%</t>
+          <t>-106.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-174.6%</t>
+          <t>-176.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.8%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-66.2%</t>
+          <t>-37.1%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2037"/>
+  <dimension ref="A1:G2036"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47798,16 +47798,16 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647104</v>
+        <v>3.780973053504659</v>
       </c>
       <c r="C2011" t="n">
         <v>3.533162878843719</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.193459850951299</v>
+        <v>-3.157877427583585</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.255422514149451</v>
+        <v>2.269655483496537</v>
       </c>
       <c r="F2011" t="n">
         <v>0.623874409742177</v>
@@ -47821,16 +47821,16 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763532</v>
+        <v>3.751680267083168</v>
       </c>
       <c r="C2012" t="n">
         <v>3.533162878843719</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.195021493766159</v>
+        <v>-3.159439070398445</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.254797857023508</v>
+        <v>2.269030826370593</v>
       </c>
       <c r="F2012" t="n">
         <v>0.623874409742177</v>
@@ -47844,16 +47844,16 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392116</v>
+        <v>3.717617470711752</v>
       </c>
       <c r="C2013" t="n">
         <v>3.531686919970721</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.222922280875632</v>
+        <v>-3.187339857507918</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.242161583306721</v>
+        <v>2.256394552653806</v>
       </c>
       <c r="F2013" t="n">
         <v>0.5892774855992422</v>
@@ -47867,16 +47867,16 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172527</v>
+        <v>3.686693354492163</v>
       </c>
       <c r="C2014" t="n">
         <v>3.528451363947919</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.345448383578526</v>
+        <v>-3.309865960210812</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.189915586202762</v>
+        <v>2.204148555549847</v>
       </c>
       <c r="F2014" t="n">
         <v>0.4667513828963483</v>
@@ -47890,16 +47890,16 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971078</v>
+        <v>3.621145657290714</v>
       </c>
       <c r="C2015" t="n">
         <v>3.595157323538423</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.365509704855033</v>
+        <v>-3.329927281487319</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.248597017282663</v>
+        <v>2.262829986629749</v>
       </c>
       <c r="F2015" t="n">
         <v>0.4466900616198413</v>
@@ -47913,16 +47913,16 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199805</v>
+        <v>3.642547663519442</v>
       </c>
       <c r="C2016" t="n">
         <v>3.73546904254027</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.622230522849857</v>
+        <v>-3.586648099482143</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.28622040908658</v>
+        <v>2.300453378433666</v>
       </c>
       <c r="F2016" t="n">
         <v>0.3382754874760265</v>
@@ -47936,16 +47936,16 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622236</v>
+        <v>3.670086579941872</v>
       </c>
       <c r="C2017" t="n">
         <v>3.80444931168591</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.776216940625997</v>
+        <v>-3.740634517258283</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.293606111121764</v>
+        <v>2.307839080468849</v>
       </c>
       <c r="F2017" t="n">
         <v>0.3382754874760265</v>
@@ -47959,16 +47959,16 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808528</v>
+        <v>3.621720592128164</v>
       </c>
       <c r="C2018" t="n">
         <v>3.790500513806031</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.725695036798331</v>
+        <v>-3.690112613430617</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.299866074772951</v>
+        <v>2.314099044120037</v>
       </c>
       <c r="F2018" t="n">
         <v>0.3382754874760265</v>
@@ -47982,16 +47982,16 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994893</v>
+        <v>3.658130309314529</v>
       </c>
       <c r="C2019" t="n">
         <v>3.802371002861445</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.978170190806056</v>
+        <v>-3.942587767438342</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.210746502225275</v>
+        <v>2.224979471572361</v>
       </c>
       <c r="F2019" t="n">
         <v>0.3382754874760265</v>
@@ -48005,16 +48005,16 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358298</v>
+        <v>3.675826111677934</v>
       </c>
       <c r="C2020" t="n">
         <v>3.803581537380389</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.247642992727764</v>
+        <v>-4.21206056936005</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.104167915975536</v>
+        <v>2.118400885322621</v>
       </c>
       <c r="F2020" t="n">
         <v>0.3382754874760265</v>
@@ -48028,16 +48028,16 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637086</v>
+        <v>3.665307032956722</v>
       </c>
       <c r="C2021" t="n">
         <v>3.80770327960771</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.405187064457206</v>
+        <v>-4.369604641089492</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.04527202951108</v>
+        <v>2.059504998858166</v>
       </c>
       <c r="F2021" t="n">
         <v>0.271373682335752</v>
@@ -48051,16 +48051,16 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301343</v>
+        <v>3.653946728620979</v>
       </c>
       <c r="C2022" t="n">
         <v>3.802781132343899</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.683151460040479</v>
+        <v>-4.647569036672765</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.929164124013961</v>
+        <v>1.943397093361046</v>
       </c>
       <c r="F2022" t="n">
         <v>0.1817539480502677</v>
@@ -48074,16 +48074,16 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215469</v>
+        <v>3.669759882535105</v>
       </c>
       <c r="C2023" t="n">
         <v>3.964985189042944</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.80011915267937</v>
+        <v>-4.764536729311656</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.044581103657448</v>
+        <v>2.058814073004534</v>
       </c>
       <c r="F2023" t="n">
         <v>0.1817539480502677</v>
@@ -48097,16 +48097,16 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456691</v>
+        <v>3.698337043776327</v>
       </c>
       <c r="C2024" t="n">
         <v>3.959831827006758</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.884837094900323</v>
+        <v>-4.849254671532609</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.005540564732881</v>
+        <v>2.019773534079967</v>
       </c>
       <c r="F2024" t="n">
         <v>0.09663791912222136</v>
@@ -48120,16 +48120,16 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253287</v>
+        <v>3.751841591572922</v>
       </c>
       <c r="C2025" t="n">
         <v>3.970061244575249</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.966771913169207</v>
+        <v>-4.931189489801493</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.982996054993819</v>
+        <v>1.997229024340905</v>
       </c>
       <c r="F2025" t="n">
         <v>0.08670317353514118</v>
@@ -48143,16 +48143,16 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717831</v>
+        <v>3.785430443037466</v>
       </c>
       <c r="C2026" t="n">
         <v>3.978986883031151</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.913033739768944</v>
+        <v>-4.87745131640123</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.013416962809826</v>
+        <v>2.027649932156912</v>
       </c>
       <c r="F2026" t="n">
         <v>0.1404413469354033</v>
@@ -48166,16 +48166,16 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616948</v>
+        <v>3.800094359936583</v>
       </c>
       <c r="C2027" t="n">
         <v>3.971139770275327</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.803027456291723</v>
+        <v>-4.767445032924009</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.049572363444891</v>
+        <v>2.063805332791977</v>
       </c>
       <c r="F2027" t="n">
         <v>0.1636459188526785</v>
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203663</v>
+        <v>3.787361500523298</v>
       </c>
       <c r="C2028" t="n">
         <v>3.975389780997301</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.659967880550797</v>
+        <v>-4.747801673263141</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.111046204463236</v>
+        <v>2.075912687378298</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1716593454426578</v>
+        <v>0.1482918593283378</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.078385388262896</v>
+        <v>4.064364896594304</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436929</v>
+        <v>3.779034987756564</v>
       </c>
       <c r="C2029" t="n">
         <v>3.982650663879838</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.358521155078959</v>
+        <v>-4.446354947791304</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.238885777534507</v>
+        <v>2.203752260449569</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.473106070914495</v>
+        <v>0.449738584800175</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.266514306428535</v>
+        <v>4.252493814759943</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064767</v>
+        <v>3.814433516384401</v>
       </c>
       <c r="C2030" t="n">
         <v>3.983621841632548</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.413476351522029</v>
+        <v>-4.501310144234373</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.217874876709989</v>
+        <v>2.182741359625052</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.473106070914495</v>
+        <v>0.449738584800175</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.267485484181245</v>
+        <v>4.253464992512654</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859301</v>
+        <v>3.822981758178935</v>
       </c>
       <c r="C2031" t="n">
         <v>3.984464746012303</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.362437975515508</v>
+        <v>-4.450271768227853</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.239133131492353</v>
+        <v>2.203999614407415</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.473106070914495</v>
+        <v>0.449738584800175</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.268328388561001</v>
+        <v>4.254307896892409</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354684</v>
+        <v>3.833532092674319</v>
       </c>
       <c r="C2032" t="n">
         <v>4.003502844886449</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.321298680648877</v>
+        <v>-4.409132473361222</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.274626948313151</v>
+        <v>2.239493431228213</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5142453657811259</v>
+        <v>0.4908778796668058</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.312050064355125</v>
+        <v>4.298029572686533</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.82576709308562</v>
+        <v>3.827550508405254</v>
       </c>
       <c r="C2033" t="n">
         <v>3.819686841010383</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.210692540569275</v>
+        <v>-4.29852633328162</v>
       </c>
       <c r="E2033" t="n">
-        <v>2.135053400468926</v>
+        <v>2.099919883383988</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6248515058607279</v>
+        <v>0.6014840197464079</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.194597744526821</v>
+        <v>4.180577252858228</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804703121462782</v>
+        <v>3.806486536782416</v>
       </c>
       <c r="C2034" t="n">
         <v>3.823188885084347</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.341273275100118</v>
+        <v>-4.429107067812462</v>
       </c>
       <c r="E2034" t="n">
-        <v>2.086323150730553</v>
+        <v>2.051189633645615</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4942707713298854</v>
+        <v>0.4709032852155653</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.119751347882278</v>
+        <v>4.105730856213687</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775043021218599</v>
+        <v>3.776826436538234</v>
       </c>
       <c r="C2035" t="n">
         <v>3.80761570416043</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.176776940909156</v>
+        <v>-4.264610733621501</v>
       </c>
       <c r="E2035" t="n">
-        <v>2.13654850348302</v>
+        <v>2.101414986398082</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.4942707713298854</v>
+        <v>0.4709032852155653</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.104178166958361</v>
+        <v>4.090157675289769</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,45 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821044820462767</v>
+        <v>3.823704766629952</v>
       </c>
       <c r="C2036" t="n">
         <v>3.806803414596859</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.052296460185205</v>
+        <v>-4.140130252897549</v>
       </c>
       <c r="E2036" t="n">
-        <v>2.185528406209031</v>
+        <v>2.150394889124092</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.4942707713298854</v>
+        <v>0.4709032852155653</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.103365877394791</v>
-      </c>
-    </row>
-    <row r="2037">
-      <c r="A2037" s="2" t="n">
-        <v>45499</v>
-      </c>
-      <c r="B2037" t="n">
-        <v>3.791242606924984</v>
-      </c>
-      <c r="C2037" t="n">
-        <v>3.805267014986832</v>
-      </c>
-      <c r="D2037" t="n">
-        <v>-4.052296460185205</v>
-      </c>
-      <c r="E2037" t="n">
-        <v>2.185528406209031</v>
-      </c>
-      <c r="F2037" t="n">
-        <v>0.4942707713298854</v>
-      </c>
-      <c r="G2037" t="n">
-        <v>3.7983308119732</v>
+        <v>4.089345385726199</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240726.xlsx
+++ b/tame_output/ON/bt/strategyON_20240726.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>51.7%</t>
         </is>
       </c>
     </row>
@@ -758,12 +758,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>83.7%</t>
+          <t>84.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,22 +786,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-28.1%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>72.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.0%</t>
+          <t>-75.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.2%</t>
+          <t>111.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.1%</t>
+          <t>124.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.0%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.6%</t>
+          <t>-48.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.7%</t>
+          <t>-71.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-575.6%</t>
+          <t>-562.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,16 +1084,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.5%</t>
+          <t>-34.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-47.6%</t>
+          <t>-45.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-161.2%</t>
+          <t>-163.3%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1247,11 +1247,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-9.2%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-106.6%</t>
+          <t>-91.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-176.9%</t>
+          <t>-176.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-21.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-37.1%</t>
+          <t>-62.9%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2036"/>
+  <dimension ref="A1:G2037"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43681,7 +43681,7 @@
         <v>45294</v>
       </c>
       <c r="B1832" t="n">
-        <v>3.301413393085799</v>
+        <v>3.301413393085798</v>
       </c>
       <c r="C1832" t="n">
         <v>3.130069279090508</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045692</v>
+        <v>3.317575502045691</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355689</v>
+        <v>3.311888301355688</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511403</v>
+        <v>3.367379938511402</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998559</v>
+        <v>3.367370539998558</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082123</v>
+        <v>3.299560092082122</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757921</v>
+        <v>3.29349053375792</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760739</v>
+        <v>3.293766719760738</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706667</v>
+        <v>3.298730590706666</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296834</v>
+        <v>3.299918119296833</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201485</v>
+        <v>3.295507330201484</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153004</v>
+        <v>3.258791981153003</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537424</v>
+        <v>3.271168579537423</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382189</v>
+        <v>3.272760131382188</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.25147557607462</v>
+        <v>3.251475576074619</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911638</v>
+        <v>3.233800325911637</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213494</v>
+        <v>3.223539378213493</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416044</v>
+        <v>3.231167537416043</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495496</v>
+        <v>3.278199702495495</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347052</v>
+        <v>3.299136146347051</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130014</v>
+        <v>3.287377576130013</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.31588437417824</v>
+        <v>3.315884374178239</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207809</v>
+        <v>3.305316798207808</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310977</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130942</v>
+        <v>3.311086391309419</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.3047157169709</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.300815818330518</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191732</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097815</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094111</v>
+        <v>3.37443904309411</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.40596051119928</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969587</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923079</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297742</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.44775050131761</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737164</v>
+        <v>3.503515506737163</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341307</v>
+        <v>3.503170282341306</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539458</v>
+        <v>3.501052558539457</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937496</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141699</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.818025609735649</v>
+        <v>-8.804813404801466</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3872465759527599</v>
+        <v>-0.3819616939790871</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.492449906936466</v>
+        <v>-1.514912358123934</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.244850148093368</v>
+        <v>2.231372677380887</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.851678448244122</v>
+        <v>-8.83846624330994</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3962251568717132</v>
+        <v>-0.3909402748980404</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.592863274853503</v>
+        <v>-1.615325726040971</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.189084681827581</v>
+        <v>2.175607211115101</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.778208616576674</v>
+        <v>-8.764996411642491</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.3514655227113126</v>
+        <v>-0.3461806407376393</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.519393443186055</v>
+        <v>-1.541855894373523</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.248538282321471</v>
+        <v>2.235060811608991</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.490059241608598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.953333033963217</v>
+        <v>-8.940120829029034</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.406960068918413</v>
+        <v>-0.4016751869447401</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.694517860572599</v>
+        <v>-1.716980311760067</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.158018852637062</v>
+        <v>2.144541381924581</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.187785127977707</v>
+        <v>-9.174572923043524</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.507960071425805</v>
+        <v>-0.5026751894521317</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.694517860572599</v>
+        <v>-1.716980311760067</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.150799687735466</v>
+        <v>2.137322217022986</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.292159859004153</v>
+        <v>-9.27894765406997</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5563821546103598</v>
+        <v>-0.5510972726366865</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.798892591599045</v>
+        <v>-1.821355042786512</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.081502658345622</v>
+        <v>2.068025187633141</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.34494601460448</v>
+        <v>-9.331733809670297</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5763808270119339</v>
+        <v>-0.5710959450382611</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.894568078181442</v>
+        <v>-1.91703052936891</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.025213156234741</v>
+        <v>2.01173568552226</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297395</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.470982807972769</v>
+        <v>-9.457770603038586</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.624101815730135</v>
+        <v>-0.6188169337564622</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.891778906559167</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.0430578585497</v>
+        <v>2.029580387837219</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.57367402532254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.413911036076838</v>
+        <v>-9.400698831142655</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5972827712853621</v>
+        <v>-0.5919978893116888</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.891778906559167</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.047048194236101</v>
+        <v>2.033570723523621</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158919</v>
+        <v>3.600038265158918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.555582877800958</v>
+        <v>-9.542370672866776</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6554267348737519</v>
+        <v>-0.6501418529000786</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.891778906559167</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.045572967337359</v>
+        <v>2.032095496624879</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.505992033376124</v>
+        <v>-9.492779828441941</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6205369869389457</v>
+        <v>-0.6152521049652728</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.819725610946866</v>
+        <v>-1.842188062134333</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.090380884157132</v>
+        <v>2.076903413444652</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.357073698904268</v>
+        <v>-9.343861493970085</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5740207867968863</v>
+        <v>-0.568735904823213</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.788476020211692</v>
+        <v>-1.81093847139916</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.096079504951553</v>
+        <v>2.082602034239073</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.68516138161528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.131228546184857</v>
+        <v>-9.118016341250673</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4741036526729134</v>
+        <v>-0.4688187706992397</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.769011795811997</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.13081458334006</v>
+        <v>2.117337112627579</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848438238121</v>
+        <v>3.684843823812099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.006649889847266</v>
+        <v>-8.993437684913081</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4231330455818179</v>
+        <v>-0.4178481636081441</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.769011795811997</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.131953727896119</v>
+        <v>2.118476257183638</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.059545177891552</v>
+        <v>-9.046332972957368</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4416573866374249</v>
+        <v>-0.4363725046637512</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.76405644972355</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.137560709711294</v>
+        <v>2.124083238998813</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611565</v>
+        <v>3.768951674611564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.987412002603671</v>
+        <v>-8.974199797669487</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.4070704122836357</v>
+        <v>-0.401785530309962</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.76405644972355</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.14329441394993</v>
+        <v>2.12981694323745</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955325</v>
+        <v>3.728577929955324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.916045609994024</v>
+        <v>-8.902833405059839</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3882611176336423</v>
+        <v>-0.3829762356599682</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.692690057113903</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.176376987121854</v>
+        <v>2.162899516409373</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.822586576008799</v>
+        <v>-8.809374371074615</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.36076098535246</v>
+        <v>-0.3554761033787863</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.692690057113903</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.166493505808947</v>
+        <v>2.153016035096466</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.555344775140401</v>
+        <v>-8.542132570206217</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2556988255044748</v>
+        <v>-0.2504139435308006</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.692690057113903</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.164658945309573</v>
+        <v>2.151181474597092</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.457437736463911</v>
+        <v>-8.444225531529726</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2168363250073391</v>
+        <v>-0.2115514430336654</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.602241856065878</v>
+        <v>-1.624704307253346</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.205150080252446</v>
+        <v>2.191672609539965</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.80082935409724</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.433484195487953</v>
+        <v>-8.420271990553768</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2065864024714625</v>
+        <v>-0.2013015204977884</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.578288315089921</v>
+        <v>-1.600750766277389</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.220190710983514</v>
+        <v>2.206713240271033</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017768</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.169424257165156</v>
+        <v>-8.156212052230972</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1142227433040959</v>
+        <v>-0.1089378613304222</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.336690827954592</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.365366357815439</v>
+        <v>2.351888887102959</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839721</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.462344633660318</v>
+        <v>-7.449132428726133</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1658220724375385</v>
+        <v>0.1711069544112123</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.336690827954592</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.362579324155138</v>
+        <v>2.349101853442658</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.422160335294127</v>
+        <v>-7.408948130359943</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1822394156718561</v>
+        <v>0.1875242976455298</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.274044078400934</v>
+        <v>-1.296506529588402</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.387033527062695</v>
+        <v>2.373556056350214</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.258760464354765</v>
+        <v>-7.24554825942058</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.246966185268358</v>
+        <v>0.2522510672420317</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.110644207461571</v>
+        <v>-1.133106658649039</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.484440270847069</v>
+        <v>2.470962800134588</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.025279242125166</v>
+        <v>-7.012067037190982</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.34828310299805</v>
+        <v>0.3535679849717237</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8771629852319727</v>
+        <v>-0.8996254364194405</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.632453433022681</v>
+        <v>2.6189759623102</v>
       </c>
     </row>
     <row r="1904">
@@ -45340,19 +45340,19 @@
         <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.155859013848905</v>
+        <v>3.083244556601354</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.875612851117651</v>
+        <v>-6.862400646183467</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4052574490880967</v>
+        <v>0.3379278738142202</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7842594939894367</v>
+        <v>-0.8067219451769045</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.685303317455243</v>
+        <v>2.599211389495212</v>
       </c>
     </row>
     <row r="1905">
@@ -45363,19 +45363,19 @@
         <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.151226500595932</v>
+        <v>3.078612043348381</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.743337377486765</v>
+        <v>-6.73012517255258</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4535351252874782</v>
+        <v>0.3862055500136021</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6519840203585501</v>
+        <v>-0.6744464715460179</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.760036088380802</v>
+        <v>2.673944160420771</v>
       </c>
     </row>
     <row r="1906">
@@ -45386,19 +45386,19 @@
         <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.154041561283568</v>
+        <v>3.081427104036018</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.587599044927023</v>
+        <v>-6.574386839992838</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.518645518999012</v>
+        <v>0.4513159437251355</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.5187081389862763</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.856294148604284</v>
+        <v>2.770202220644252</v>
       </c>
     </row>
     <row r="1907">
@@ -45409,19 +45409,19 @@
         <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.166947902507227</v>
+        <v>3.094333445259677</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.338599246243442</v>
+        <v>-6.325387041309257</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6311517796961028</v>
+        <v>0.5638222044222267</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.5187081389862763</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.869200489827942</v>
+        <v>2.783108561867911</v>
       </c>
     </row>
     <row r="1908">
@@ -45432,19 +45432,19 @@
         <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.038971972908008</v>
+        <v>2.966357515660458</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.444189236016546</v>
+        <v>-6.430977031082362</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4609398541876426</v>
+        <v>0.3936102789137657</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.6018356775719129</v>
+        <v>-0.6242981287593807</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.677870566364861</v>
+        <v>2.59177863840483</v>
       </c>
     </row>
     <row r="1909">
@@ -45455,19 +45455,19 @@
         <v>3.770422583987901</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.087516314785095</v>
+        <v>3.014901857537544</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.462924138135143</v>
+        <v>-6.449711933200959</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5019902352172902</v>
+        <v>0.4346606599434133</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.6074316872320442</v>
+        <v>-0.629894138419512</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.723057302445869</v>
+        <v>2.636965374485837</v>
       </c>
     </row>
     <row r="1910">
@@ -45478,19 +45478,19 @@
         <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.967637392096927</v>
+        <v>2.895022934849377</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.314984096727544</v>
+        <v>-6.30177189179336</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4412873290921624</v>
+        <v>0.3739577538182854</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.5871107713234867</v>
+        <v>-0.6095732225109545</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.615370929302836</v>
+        <v>2.529279001342804</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.958923405843449</v>
+        <v>2.886308948595898</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.262014574473556</v>
+        <v>-6.248802369539371</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4537611517402795</v>
+        <v>0.3864315764664026</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5566037002569656</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.638438656401751</v>
+        <v>2.552346728441719</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.951962793748356</v>
+        <v>2.879348336500805</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.218466167702865</v>
+        <v>-6.205253962768681</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4642199023534626</v>
+        <v>0.3968903270795856</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5566037002569656</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.631478044306657</v>
+        <v>2.545386116346626</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.966425148129499</v>
+        <v>2.893810690881948</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.185102961224096</v>
+        <v>-6.171890756289912</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4920275393261129</v>
+        <v>0.4246979640522364</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5566037002569656</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.645940398687801</v>
+        <v>2.559848470727769</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.960957268588694</v>
+        <v>2.888342811341143</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.076843824101575</v>
+        <v>-6.06363161916739</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5298633146343166</v>
+        <v>0.4625337393604401</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5566037002569656</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.640472519146996</v>
+        <v>2.554380591186964</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.958455362599271</v>
+        <v>2.88584090535172</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.953552689284444</v>
+        <v>-5.940340484350259</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5766778625717461</v>
+        <v>0.5093482872978692</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.4108501142523673</v>
+        <v>-0.4333125654398351</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.711945294047851</v>
+        <v>2.625853366087819</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.966156340836596</v>
+        <v>2.893541883589045</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.932403490381001</v>
+        <v>-5.919191285446816</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5928385203704485</v>
+        <v>0.5255089450965715</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.3897009153489239</v>
+        <v>-0.4121633665363917</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.732335791627242</v>
+        <v>2.646243863667211</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.961937049183647</v>
+        <v>2.889322591936096</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.688638048397556</v>
+        <v>-5.675425843463372</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.686125405510877</v>
+        <v>0.618795830237</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.3897009153489239</v>
+        <v>-0.4121633665363917</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.728116499974293</v>
+        <v>2.642024572014261</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824311233057524</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.964061363103663</v>
+        <v>2.891446905856112</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.586875228120261</v>
+        <v>-5.573663023186077</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7289548475418108</v>
+        <v>0.6616252722679339</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.398944298143963</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.738172254929766</v>
+        <v>2.652080326969735</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.956803438087365</v>
+        <v>2.884188980839814</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.337024834171187</v>
+        <v>-5.323812629237002</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8216370801051429</v>
+        <v>0.754307504831266</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.398944298143963</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.730914329913468</v>
+        <v>2.644822401953437</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.960402561608014</v>
+        <v>2.887788104360463</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.161132741703755</v>
+        <v>-5.14792053676957</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8955930406127646</v>
+        <v>0.8282634653388876</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.398944298143963</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.734513453434117</v>
+        <v>2.648421525474085</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780933911392984</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.973730067662567</v>
+        <v>2.901115610415017</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.989686278681291</v>
+        <v>-4.976474073747107</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9774991318763036</v>
+        <v>0.9101695566024266</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.2050353839340321</v>
+        <v>-0.2274978351214999</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.850708837302149</v>
+        <v>2.764616909342117</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.972750545278864</v>
+        <v>2.900136088031314</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.915396712942952</v>
+        <v>-4.902184508008768</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.006235435787936</v>
+        <v>0.9389058605140592</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.1307458181956928</v>
+        <v>-0.1532082693831606</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.894303054361449</v>
+        <v>2.808211126401417</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.977445346333182</v>
+        <v>2.904830889085631</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.851760970709018</v>
+        <v>-4.838548765774833</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.036384533735827</v>
+        <v>0.9690549584619503</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.06711007596175828</v>
+        <v>-0.08957252714922609</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.937179300756127</v>
+        <v>2.851087372796095</v>
       </c>
     </row>
     <row r="1924">
@@ -45800,19 +45800,19 @@
         <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.958639605116977</v>
+        <v>2.886025147869427</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.740334211383098</v>
+        <v>-4.727122006448913</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.062149496249991</v>
+        <v>0.9948199209761142</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.06711007596175828</v>
+        <v>-0.08957252714922609</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.918373559539923</v>
+        <v>2.832281631579891</v>
       </c>
     </row>
     <row r="1925">
@@ -45823,19 +45823,19 @@
         <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.960382681741855</v>
+        <v>2.887768224494304</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.499903714578237</v>
+        <v>-4.486691509644053</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.160064771596812</v>
+        <v>1.092735196322935</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.173320420843102</v>
+        <v>0.1508579696556342</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.064374934247716</v>
+        <v>2.978283006287685</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.964311995576675</v>
+        <v>2.891697538329124</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.427661146407043</v>
+        <v>-4.414448941472858</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.192891112700111</v>
+        <v>1.125561537426234</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.173320420843102</v>
+        <v>0.1508579696556342</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.068304248082536</v>
+        <v>2.982212320122505</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.964990579494015</v>
+        <v>2.892376122246464</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.409947459529177</v>
+        <v>-4.396735254594993</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.200655171368597</v>
+        <v>1.13332559609472</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.1765017497400188</v>
+        <v>0.154039298552551</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.070891629338026</v>
+        <v>2.984799701377995</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.961988650714008</v>
+        <v>2.889374193466458</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.30114257404945</v>
+        <v>-4.287930369115266</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.241175196780481</v>
+        <v>1.173845621506604</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.1765017497400188</v>
+        <v>0.154039298552551</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.06788970055802</v>
+        <v>2.981797772597989</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.963567687724622</v>
+        <v>2.890953230477072</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.08112177601244</v>
+        <v>-4.067909571078255</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.330762553005899</v>
+        <v>1.263432977732022</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3177215948079991</v>
+        <v>0.2952591436205312</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.154200644609422</v>
+        <v>3.068108716649391</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.979461870526446</v>
+        <v>2.906847413278895</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.948254086949162</v>
+        <v>-3.935041882014977</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.399803811433034</v>
+        <v>1.332474236159157</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3177215948079991</v>
+        <v>0.2952591436205312</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.170094827411245</v>
+        <v>3.084002899451214</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.980607714966748</v>
+        <v>2.907993257719197</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.828081003584662</v>
+        <v>-3.814868798650478</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.449018889219135</v>
+        <v>1.381689313945258</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.437894678172498</v>
+        <v>0.4154322269850302</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.243344521870247</v>
+        <v>3.157252593910215</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.990695817528187</v>
+        <v>2.918081360280637</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.683408858484925</v>
+        <v>-3.67019665355074</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.51697584982047</v>
+        <v>1.449646274546593</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.5825668232722354</v>
+        <v>0.5601043720847676</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.340235911491529</v>
+        <v>3.254143983531498</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.976733308929613</v>
+        <v>2.904118851682063</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.743283685842617</v>
+        <v>-3.730071480908433</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.479063410278819</v>
+        <v>1.411733835004942</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5226919959145433</v>
+        <v>0.5002295447270755</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.29034850647834</v>
+        <v>3.204256578518308</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.992022478163822</v>
+        <v>2.919408020916271</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.62346345493178</v>
+        <v>-3.610251249997595</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.542280671877363</v>
+        <v>1.474951096603486</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5226919959145433</v>
+        <v>0.5002295447270755</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.305637675712548</v>
+        <v>3.219545747752517</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.899666677486263</v>
+        <v>2.827052220238713</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.625933161393586</v>
+        <v>-3.612720956459401</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.448936988615082</v>
+        <v>1.381607413341205</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5202222894527371</v>
+        <v>0.4977598382652693</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.211800051157906</v>
+        <v>3.125708123197874</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.743220196003599</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.818928538971565</v>
+        <v>2.746314081724014</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.694303347717596</v>
+        <v>-3.681091142783411</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.340850775570779</v>
+        <v>1.273521200296902</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.529497988488952</v>
+        <v>0.5070355373014842</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.136627332064936</v>
+        <v>3.050535404104905</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.809365247603456</v>
+        <v>2.736750790355905</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.708091400564642</v>
+        <v>-3.694879195630458</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.325772263063852</v>
+        <v>1.258442687789975</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.529497988488952</v>
+        <v>0.5070355373014842</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.127064040696828</v>
+        <v>3.040972112736796</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.946396084295658</v>
+        <v>2.873781627048108</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.763611476457232</v>
+        <v>-3.750399271523047</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.440595069399018</v>
+        <v>1.373265494125142</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.529497988488952</v>
+        <v>0.5070355373014842</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.26409487738903</v>
+        <v>3.178002949428999</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.950963316287446</v>
+        <v>2.878348859039896</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.588137216664763</v>
+        <v>-3.574925011730578</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.515352005307794</v>
+        <v>1.448022430033917</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.529497988488952</v>
+        <v>0.5070355373014842</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.268662109380818</v>
+        <v>3.182570181420787</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.926705345048653</v>
+        <v>2.854090887801103</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.699073469306011</v>
+        <v>-3.685861264371827</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.446719533012502</v>
+        <v>1.379389957738625</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.529497988488952</v>
+        <v>0.5070355373014842</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.244404138142025</v>
+        <v>3.158312210181994</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.855243658450103</v>
+        <v>2.782629201202552</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.665409923833729</v>
+        <v>-3.652197718899545</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.388723264602864</v>
+        <v>1.321393689328987</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5631615339612339</v>
+        <v>0.5406990827737661</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.193140578826844</v>
+        <v>3.107048650866812</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264163</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.865416044882235</v>
+        <v>2.792801587634685</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.605557304630006</v>
+        <v>-3.592345099695822</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.422836698716486</v>
+        <v>1.355507123442609</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5631615339612339</v>
+        <v>0.5406990827737661</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.203312965258976</v>
+        <v>3.117221037298945</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.860362315456096</v>
+        <v>2.787747858208545</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.519313841603629</v>
+        <v>-3.506101636669444</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.452280354500897</v>
+        <v>1.38495077922702</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5631615339612339</v>
+        <v>0.5406990827737661</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.198259235832837</v>
+        <v>3.112167307872805</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.852138090900621</v>
+        <v>2.779523633653071</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.564620661002609</v>
+        <v>-3.551408456068424</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.425933402185831</v>
+        <v>1.358603826911954</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5223513709520031</v>
+        <v>0.4998889197645353</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.165548913471823</v>
+        <v>3.079456985511792</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.852689963933723</v>
+        <v>2.780075506686172</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.59365376570491</v>
+        <v>-3.580441560770726</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.414872033338011</v>
+        <v>1.347542458064135</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5223513709520031</v>
+        <v>0.4998889197645353</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.166100786504925</v>
+        <v>3.080008858544894</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.781962655825089</v>
+        <v>2.709348198577538</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.500843284254051</v>
+        <v>-3.487631079319867</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.381268917809721</v>
+        <v>1.313939342535844</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6151618524028625</v>
+        <v>0.5926994012153947</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.151059767266806</v>
+        <v>3.064967839306775</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.783836131749689</v>
+        <v>2.711221674502139</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.545232753583479</v>
+        <v>-3.532020548649294</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.365386606002551</v>
+        <v>1.298057030728674</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.5707723830734348</v>
+        <v>0.548309931885967</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.126299561593751</v>
+        <v>3.040207633633719</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.778911840261412</v>
+        <v>2.706297383013862</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.432561535347229</v>
+        <v>-3.419349330413044</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.405530801808774</v>
+        <v>1.338201226534897</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.683443601309685</v>
+        <v>0.6609811501222171</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.188978001047224</v>
+        <v>3.102886073087192</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.78440313609208</v>
+        <v>2.711788678844529</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.320184534164556</v>
+        <v>-3.306972329230371</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.45597289811251</v>
+        <v>1.388643322838633</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.683443601309685</v>
+        <v>0.6609811501222171</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.194469296877891</v>
+        <v>3.108377368917859</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.795900337860619</v>
+        <v>2.723285880613068</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.347964932065909</v>
+        <v>-3.334752727131725</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.456357940720508</v>
+        <v>1.389028365446631</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6556632034083318</v>
+        <v>0.633200752220864</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.189298259905618</v>
+        <v>3.103206331945587</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.634256057861272</v>
+        <v>2.561641600613721</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.466345604796047</v>
+        <v>-3.453133399861863</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.247361391629106</v>
+        <v>1.180031816355229</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5884453512573556</v>
+        <v>0.5659829000698878</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.987323268615686</v>
+        <v>2.901231340655654</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.754405718580478</v>
+        <v>2.681791261332927</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.574959683239379</v>
+        <v>-3.561747478305194</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.324065420970979</v>
+        <v>1.256735845697102</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5884453512573556</v>
+        <v>0.5659829000698878</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.107472929334891</v>
+        <v>3.02138100137486</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.768918744682801</v>
+        <v>2.69630428743525</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.539550644991236</v>
+        <v>-3.526338440057051</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.352742062372559</v>
+        <v>1.285412487098682</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5884453512573556</v>
+        <v>0.5659829000698878</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.121985955437214</v>
+        <v>3.035894027477183</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.766338186025169</v>
+        <v>2.693723728777619</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.501166982433085</v>
+        <v>-3.4879547774989</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.365514968738188</v>
+        <v>1.298185393464311</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6268290138155068</v>
+        <v>0.604366562628039</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.142435594314474</v>
+        <v>3.056343666354442</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.763067214870471</v>
+        <v>2.69045275762292</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.324050652397919</v>
+        <v>-3.310838447463734</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.433090529597556</v>
+        <v>1.365760954323679</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6268290138155068</v>
+        <v>0.604366562628039</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.139164623159775</v>
+        <v>3.053072695199744</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.763750606632384</v>
+        <v>2.691136149384834</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.369142897231464</v>
+        <v>-3.35593069229728</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.415737023426051</v>
+        <v>1.348407448152174</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.564932970646117</v>
+        <v>0.5424705194586492</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.102710389020055</v>
+        <v>3.016618461060023</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.757537581938799</v>
+        <v>2.684923124691248</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.189767475992697</v>
+        <v>-3.176555271058512</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.481274167227973</v>
+        <v>1.413944591954096</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7217097288168357</v>
+        <v>0.6992472776293679</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.190563419228901</v>
+        <v>3.104471491268869</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.738345037270388</v>
+        <v>2.665730580022838</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.234781689513303</v>
+        <v>-3.221569484579118</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.44407593715132</v>
+        <v>1.376746361877443</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6913608335022311</v>
+        <v>0.6688983823147633</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.153161537371727</v>
+        <v>3.067069609411696</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.744036599609334</v>
+        <v>2.671422142361783</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.501786199785738</v>
+        <v>-3.488573994851554</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.342965695381292</v>
+        <v>1.275636120107415</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4969977954592826</v>
+        <v>0.4745353442718147</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.042235276884904</v>
+        <v>2.956143348924873</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760813</v>
+        <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.743240521505836</v>
+        <v>2.670626064258285</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.602983981222911</v>
+        <v>-3.589771776288726</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.301690504702924</v>
+        <v>1.234360929429047</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4285889819139634</v>
+        <v>0.4061265307264955</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.000393910654214</v>
+        <v>2.914301982694183</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.740840483060152</v>
+        <v>2.668226025812602</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.596473014608598</v>
+        <v>-3.583260809674414</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.301894852902966</v>
+        <v>1.234565277629089</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4285889819139634</v>
+        <v>0.4061265307264955</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.99799387220853</v>
+        <v>2.911901944248499</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.737365202268397</v>
+        <v>2.664750745020847</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.577434886901301</v>
+        <v>-3.564222681967117</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.306034823194129</v>
+        <v>1.238705247920253</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3704053705827688</v>
+        <v>0.347942919395301</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.959608424618059</v>
+        <v>2.873516496658028</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.914947071207078</v>
+        <v>2.842332613959527</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.608561518051919</v>
+        <v>-3.595349313117735</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.471166039672563</v>
+        <v>1.403836464398686</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3704053705827688</v>
+        <v>0.347942919395301</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.137190293556739</v>
+        <v>3.051098365596708</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067865</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.915780400193211</v>
+        <v>2.843165942945661</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.622428279385836</v>
+        <v>-3.609216074451652</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.466452664125129</v>
+        <v>1.399123088851252</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3325474538489459</v>
+        <v>0.310085002661478</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.115308872502579</v>
+        <v>3.029216944542548</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.921788930590137</v>
+        <v>2.849174473342587</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.577624107845907</v>
+        <v>-3.564411902911722</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.490382863138027</v>
+        <v>1.42305328786415</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3325474538489459</v>
+        <v>0.310085002661478</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.121317402899505</v>
+        <v>3.035225474939474</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.819739151867337</v>
+        <v>2.747124694619786</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.429881137610904</v>
+        <v>-3.41666893267672</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.447430272509228</v>
+        <v>1.380100697235351</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5003548110838291</v>
+        <v>0.4778923598963612</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.119952038517634</v>
+        <v>3.033860110557603</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181171</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.822532773398818</v>
+        <v>2.749918316151267</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.531895820142125</v>
+        <v>-3.518683615207941</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.40941802102822</v>
+        <v>1.342088445754343</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5003548110838291</v>
+        <v>0.4778923598963612</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.122745660049115</v>
+        <v>3.036653732089084</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.823195121790476</v>
+        <v>2.750580664542925</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.525743114089341</v>
+        <v>-3.512530909155156</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.412541451840992</v>
+        <v>1.345211876567115</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5065075171366133</v>
+        <v>0.4840450659491455</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.127099632072444</v>
+        <v>3.041007704112413</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.822275598530586</v>
+        <v>2.749661141283036</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.542552412239842</v>
+        <v>-3.529340207305658</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.404898209320902</v>
+        <v>1.337568634047025</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4896982189861117</v>
+        <v>0.4672357677986438</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.116094529922254</v>
+        <v>3.030002601962222</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.888611152327407</v>
+        <v>2.815996695079857</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.480254413463721</v>
+        <v>-3.467042208529536</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.496152962628172</v>
+        <v>1.428823387354295</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4896982189861117</v>
+        <v>0.4672357677986438</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.182430083719074</v>
+        <v>3.096338155759043</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.690903154041534</v>
+        <v>2.618288696793984</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.278464215798563</v>
+        <v>-3.265252010864378</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.379161043408362</v>
+        <v>1.311831468134485</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.687716411155266</v>
+        <v>0.6652539599677982</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.103533000734694</v>
+        <v>3.017441072774663</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852426</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.761193386363709</v>
+        <v>2.688578929116159</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.329350928484757</v>
+        <v>-3.316138723550573</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.429096590656059</v>
+        <v>1.361767015382182</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.6368296984690716</v>
+        <v>0.6143672472816037</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.143291205445153</v>
+        <v>3.057199277485121</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.775821122479753</v>
+        <v>2.703206665232202</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.427091473109732</v>
+        <v>-3.413879268175547</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.404628108922113</v>
+        <v>1.337298533648236</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6209404203360913</v>
+        <v>0.5984779691486235</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.148385374681408</v>
+        <v>3.062293446721377</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489384</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.774357103304425</v>
+        <v>2.701742646056874</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.487300771115016</v>
+        <v>-3.474088566180832</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.379080370544671</v>
+        <v>1.311750795270794</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5607311223308068</v>
+        <v>0.538268671143339</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.110795776702909</v>
+        <v>3.024703848742878</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.772848721344353</v>
+        <v>2.700234264096803</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.410878724683089</v>
+        <v>-3.397666519748905</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.40814080715737</v>
+        <v>1.340811231883493</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5607311223308068</v>
+        <v>0.538268671143339</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.109287394742838</v>
+        <v>3.023195466782806</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316248</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.77271158877979</v>
+        <v>2.700097131532239</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.366505593044521</v>
+        <v>-3.353293388110336</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.425752927248234</v>
+        <v>1.358423351974357</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.6051042539693754</v>
+        <v>0.5826418027819076</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.135774141161415</v>
+        <v>3.049682213201383</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105967</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.76710538291838</v>
+        <v>2.694490925670829</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.388985943903406</v>
+        <v>-3.375773738969221</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.411154581043271</v>
+        <v>1.343825005769394</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.6051042539693754</v>
+        <v>0.5826418027819076</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.130167935300006</v>
+        <v>3.044076007339974</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833011148190325</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.773487139946185</v>
+        <v>2.700872682698634</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.34133021334235</v>
+        <v>-3.328118008408166</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.436598630295497</v>
+        <v>1.36926905502162</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.652759984530431</v>
+        <v>0.6302975333429632</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.165143130664444</v>
+        <v>3.079051202704412</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.778379513320909</v>
+        <v>2.705765056073359</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.240812054843595</v>
+        <v>-3.227599849909411</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.481698267069724</v>
+        <v>1.414368691795847</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7532781430291856</v>
+        <v>0.7308156918417178</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.230346399138421</v>
+        <v>3.14425447117839</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.765134185796782</v>
+        <v>2.692519728549231</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.301478645245985</v>
+        <v>-3.2882664403118</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.444186303384641</v>
+        <v>1.376856728110764</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6715798263106519</v>
+        <v>0.6491173751231841</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.168082081583173</v>
+        <v>3.081990153623142</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816837033932768</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.76923188840741</v>
+        <v>2.69661743115986</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.256640243637587</v>
+        <v>-3.243428038703402</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.466219366638629</v>
+        <v>1.398889791364752</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6761232592555214</v>
+        <v>0.6536608080680536</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.174905843960723</v>
+        <v>3.088813916000692</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.773392828038488</v>
+        <v>2.700778370790938</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.276138699879595</v>
+        <v>-3.26292649494541</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.462580923772903</v>
+        <v>1.395251348499026</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6280386179756171</v>
+        <v>0.6055761667881493</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.150215998823859</v>
+        <v>3.064124070863827</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.779272430566325</v>
+        <v>2.706657973318775</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.231935862793694</v>
+        <v>-3.21872365785951</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.4861416611351</v>
+        <v>1.418812085861224</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6722414550615176</v>
+        <v>0.6497790038740497</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.182617303603236</v>
+        <v>3.096525375643205</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.777682431035573</v>
+        <v>2.705067973788022</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.268914890457137</v>
+        <v>-3.255702685522953</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.469760050538971</v>
+        <v>1.402430475265094</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7092153568528481</v>
+        <v>0.6867529056653803</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.203211645147282</v>
+        <v>3.117119717187251</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.828930196218613</v>
+        <v>2.756315738971062</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.110623472917865</v>
+        <v>-3.097411267983681</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.584324382737719</v>
+        <v>1.516994807463842</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7092153568528481</v>
+        <v>0.6867529056653803</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.254459410330322</v>
+        <v>3.16836748237029</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.827370900812866</v>
+        <v>2.754756443565315</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.902981469283389</v>
+        <v>-2.889769264349205</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.665821888785763</v>
+        <v>1.598492313511886</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9168573604873242</v>
+        <v>0.8943949092998564</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.37748531710526</v>
+        <v>3.291393389145229</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.822319129051136</v>
+        <v>2.749704671803585</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.851949376560861</v>
+        <v>-2.838737171626676</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.681182954113044</v>
+        <v>1.613853378839167</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9678894532098522</v>
+        <v>0.9454270020223844</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.403052800977047</v>
+        <v>3.316960873017016</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.839506533143841</v>
+        <v>2.76689207589629</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.786725195433656</v>
+        <v>-2.773512990499471</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.724460030656631</v>
+        <v>1.657130455382754</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.033113634337058</v>
+        <v>1.01065118314959</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.459374713746076</v>
+        <v>3.373282785786044</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840061186882557</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.835467505443121</v>
+        <v>2.76285304819557</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.749298175362522</v>
+        <v>-2.736085970428337</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.735391810984365</v>
+        <v>1.668062235710488</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.038365172366239</v>
+        <v>1.015902721178771</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.458486608862865</v>
+        <v>3.372394680902834</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.836724297774361</v>
+        <v>2.764109840526811</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.76940983139723</v>
+        <v>-2.756197626463046</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.728603940901722</v>
+        <v>1.661274365627845</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.049392517363658</v>
+        <v>1.026930066176191</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.466359808192557</v>
+        <v>3.380267880232525</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.997282068795572</v>
+        <v>2.924667611548021</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.715665016970025</v>
+        <v>-2.702452812035841</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.910659637693815</v>
+        <v>1.843330062419938</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.059455826804121</v>
+        <v>1.036993375616653</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.632955564878045</v>
+        <v>3.546863636918014</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.117394978013389</v>
+        <v>3.044780520765839</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.640882755945013</v>
+        <v>-2.627670551010828</v>
       </c>
       <c r="E1992" t="n">
-        <v>2.060685451321637</v>
+        <v>1.99335587604776</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.134238087829133</v>
+        <v>1.111775636641665</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.79793783071087</v>
+        <v>3.711845902750838</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814230727998755</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.109102954027248</v>
+        <v>3.036488496779698</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.614798671681205</v>
+        <v>-2.60158646674702</v>
       </c>
       <c r="E1993" t="n">
-        <v>2.062827061041019</v>
+        <v>1.995497485767142</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.134238087829133</v>
+        <v>1.111775636641665</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.789645806724729</v>
+        <v>3.703553878764697</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.107296149611028</v>
+        <v>3.034681692363477</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.536667490832258</v>
+        <v>-2.523455285898073</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.092272728964377</v>
+        <v>2.024943153690501</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.208414898712818</v>
+        <v>1.18595244752535</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.832345088838719</v>
+        <v>3.746253160878688</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.124850555337819</v>
+        <v>3.052236098090269</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.527775029438975</v>
+        <v>-2.51456282450479</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.113384119248482</v>
+        <v>2.046054543974605</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.208414898712818</v>
+        <v>1.18595244752535</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.84989949456551</v>
+        <v>3.763807566605479</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.116705602742403</v>
+        <v>3.044091145494852</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.696251146408853</v>
+        <v>-2.683038941474668</v>
       </c>
       <c r="E1996" t="n">
-        <v>2.037848719865115</v>
+        <v>1.970519144591238</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.180467062996237</v>
+        <v>1.158004611808769</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.824985840540146</v>
+        <v>3.738893912580114</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.097975299930265</v>
+        <v>3.025360842682714</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.99845161754727</v>
+        <v>-1.985239412613085</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.29823822859761</v>
+        <v>2.230908653323733</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.110119003625826</v>
+        <v>1.087656552438359</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.764046702105761</v>
+        <v>3.677954774145729</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.08863932242717</v>
+        <v>3.016024865179619</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.975730513864117</v>
+        <v>-1.962518308929933</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.297990692567776</v>
+        <v>2.230661117293899</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.110119003625826</v>
+        <v>1.087656552438359</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.754710724602666</v>
+        <v>3.668618796642634</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.247545448278339</v>
+        <v>3.174930991030788</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.104932327158159</v>
+        <v>-2.091720122223975</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.405216093101328</v>
+        <v>2.337886517827451</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9809171903317842</v>
+        <v>0.9584547391443163</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.836095762477409</v>
+        <v>3.750003834517378</v>
       </c>
     </row>
     <row r="2000">
@@ -47548,19 +47548,19 @@
         <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.284623270771985</v>
+        <v>3.212008813524434</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.259713333936415</v>
+        <v>-2.246501129002231</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.380381512883672</v>
+        <v>2.313051937609795</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.947549516277308</v>
+        <v>0.9250870650898402</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.85315298053837</v>
+        <v>3.767061052578339</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.28129862676153</v>
+        <v>3.20868416951398</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.252658643721241</v>
+        <v>-2.239446438787057</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.379878744959286</v>
+        <v>2.312549169685409</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9546042064924818</v>
+        <v>0.932141755305014</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.854061150657019</v>
+        <v>3.767969222696988</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.291304780406272</v>
+        <v>3.218690323158721</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.225707419394753</v>
+        <v>-2.212495214460569</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.400665388334623</v>
+        <v>2.333335813060746</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9694845525202009</v>
+        <v>0.9470221013327331</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.872995511918393</v>
+        <v>3.786903583958361</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.475407912551232</v>
+        <v>3.402793455303681</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.36166042745107</v>
+        <v>-2.348448222516885</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.530387317257056</v>
+        <v>2.46305774198318</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9694845525202009</v>
+        <v>0.9470221013327331</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.057098644063353</v>
+        <v>3.971006716103321</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.467524607454225</v>
+        <v>3.394910150206674</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.384068545255942</v>
+        <v>-2.370856340321757</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.513540765038101</v>
+        <v>2.446211189764224</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9694845525202009</v>
+        <v>0.9470221013327331</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.049215338966346</v>
+        <v>3.963123411006314</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.469578607003862</v>
+        <v>3.396964149756311</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.532074312735341</v>
+        <v>-2.518862107801157</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.456392457595978</v>
+        <v>2.389062882322102</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.8827575436566595</v>
+        <v>0.8602950924691917</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.999233133197858</v>
+        <v>3.913141205237826</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.729452285161975</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.525832324725709</v>
+        <v>3.453217867478159</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.541515238623871</v>
+        <v>-2.528303033689687</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.508869804962414</v>
+        <v>2.441540229688536</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.005184661200051</v>
+        <v>0.9827222100125831</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.12894312144574</v>
+        <v>4.042851193485709</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.714941193321632</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.52872341927101</v>
+        <v>3.45610896202346</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.593788845959513</v>
+        <v>-2.580576641025328</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.490851456573458</v>
+        <v>2.423521881299581</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9529110538644098</v>
+        <v>0.9304486026769418</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.100470051589657</v>
+        <v>4.014378123629625</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.526835232164785</v>
+        <v>3.454220774917235</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.670118823560419</v>
+        <v>-2.656906618626234</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.458431278426871</v>
+        <v>2.391101703152994</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9529110538644098</v>
+        <v>0.9304486026769418</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.098581864483432</v>
+        <v>4.0124899365234</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.521655461767648</v>
+        <v>3.449041004520097</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.872372543884772</v>
+        <v>-2.859160338950587</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.372350019899992</v>
+        <v>2.305020444626115</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.7506573335400564</v>
+        <v>0.7281948823525883</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.972049861891682</v>
+        <v>3.88595793393165</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.5200894719778</v>
+        <v>3.447475014730249</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.033940969412027</v>
+        <v>-3.020728764477842</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.306156659899242</v>
+        <v>2.238827084625365</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.623874409742177</v>
+        <v>0.601411958554709</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.894414117823106</v>
+        <v>3.808322189863075</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.780973053504659</v>
+        <v>3.754911907647104</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.533162878843719</v>
+        <v>3.460548421596168</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.157877427583585</v>
+        <v>-3.153030056575396</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.269655483496537</v>
+        <v>2.198979974652262</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.623874409742177</v>
+        <v>0.601411958554709</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.907487524689025</v>
+        <v>3.821395596728994</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.751680267083168</v>
+        <v>3.749896851763531</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.533162878843719</v>
+        <v>3.460548421596168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.159439070398445</v>
+        <v>-3.154591699390256</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.269030826370593</v>
+        <v>2.198355317526318</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.623874409742177</v>
+        <v>0.601411958554709</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.907487524689025</v>
+        <v>3.821395596728994</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.717617470711752</v>
+        <v>3.715834055392115</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.531686919970721</v>
+        <v>3.45907246272317</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.187339857507918</v>
+        <v>-3.182492486499729</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.256394552653806</v>
+        <v>2.185719043809531</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5892774855992422</v>
+        <v>0.5668150344117742</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.885253411330266</v>
+        <v>3.799161483370235</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.686693354492163</v>
+        <v>3.684909939172526</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.528451363947919</v>
+        <v>3.455836906700369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.309865960210812</v>
+        <v>-3.305018589202623</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.204148555549847</v>
+        <v>2.133473046705572</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4667513828963483</v>
+        <v>0.4442889317088803</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.808502193685729</v>
+        <v>3.722410265725697</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.621145657290714</v>
+        <v>3.619362241971077</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.595157323538423</v>
+        <v>3.522542866290872</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.329927281487319</v>
+        <v>-3.32507991047913</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.262829986629749</v>
+        <v>2.192154477785473</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4466900616198413</v>
+        <v>0.4242276104323733</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.863171360510328</v>
+        <v>3.777079432550297</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.642547663519442</v>
+        <v>3.640764248199805</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.73546904254027</v>
+        <v>3.662854585292719</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.586648099482143</v>
+        <v>-3.581800728473953</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.300453378433666</v>
+        <v>2.229777869589391</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3382754874760265</v>
+        <v>0.3158130362885584</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.938434335025886</v>
+        <v>3.852342407065855</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.670086579941872</v>
+        <v>3.668303164622235</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.80444931168591</v>
+        <v>3.731834854438359</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.740634517258283</v>
+        <v>-3.735787146250094</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.307839080468849</v>
+        <v>2.237163571624574</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3382754874760265</v>
+        <v>0.3158130362885584</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.007414604171526</v>
+        <v>3.921322676211495</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.621720592128164</v>
+        <v>3.619937176808527</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.790500513806031</v>
+        <v>3.71788605655848</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.690112613430617</v>
+        <v>-3.685265242422428</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.314099044120037</v>
+        <v>2.243423535275761</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3382754874760265</v>
+        <v>0.3158130362885584</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.993465806291647</v>
+        <v>3.907373878331616</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.658130309314529</v>
+        <v>3.656346893994892</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.802371002861445</v>
+        <v>3.729756545613894</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.942587767438342</v>
+        <v>-3.937740396430153</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.224979471572361</v>
+        <v>2.154303962728086</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3382754874760265</v>
+        <v>0.3158130362885584</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.005336295347061</v>
+        <v>3.919244367387029</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.675826111677934</v>
+        <v>3.674042696358297</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.803581537380389</v>
+        <v>3.730967080132838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.21206056936005</v>
+        <v>-4.207213198351861</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.118400885322621</v>
+        <v>2.047725376478346</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3382754874760265</v>
+        <v>0.3158130362885584</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.006546829866005</v>
+        <v>3.920454901905973</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.665307032956722</v>
+        <v>3.663523617637085</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.80770327960771</v>
+        <v>3.735088822360159</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.369604641089492</v>
+        <v>-4.364757270081302</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.059504998858166</v>
+        <v>1.988829490013891</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.271373682335752</v>
+        <v>0.248911231148284</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.970527489009162</v>
+        <v>3.88443556104913</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.653946728620979</v>
+        <v>3.652163313301342</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.802781132343899</v>
+        <v>3.730166675096349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.647569036672765</v>
+        <v>-4.642721665664576</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.943397093361046</v>
+        <v>1.872721584516771</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.1817539480502677</v>
+        <v>0.1592914968627997</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.91183350117406</v>
+        <v>3.825741573214029</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.669759882535105</v>
+        <v>3.667976467215468</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.964985189042944</v>
+        <v>3.892370731795393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.764536729311656</v>
+        <v>-4.759689358303467</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.058814073004534</v>
+        <v>1.988138564160259</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.1817539480502677</v>
+        <v>0.1592914968627997</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.074037557873105</v>
+        <v>3.987945629913073</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.698337043776327</v>
+        <v>3.69655362845669</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.959831827006758</v>
+        <v>3.887217369759207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.849254671532609</v>
+        <v>-4.84440730052442</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.019773534079967</v>
+        <v>1.949098025235692</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.09663791912222136</v>
+        <v>0.07417546793475333</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.017814578480091</v>
+        <v>3.931722650520059</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.751841591572922</v>
+        <v>3.750058176253286</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.970061244575249</v>
+        <v>3.897446787327698</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.931189489801493</v>
+        <v>-4.926342118793303</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.997229024340905</v>
+        <v>1.92655351549663</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.08670317353514118</v>
+        <v>0.06424072234767314</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.022083148696334</v>
+        <v>3.935991220736303</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.785430443037466</v>
+        <v>3.78364702771783</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.978986883031151</v>
+        <v>3.906372425783601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.87745131640123</v>
+        <v>-4.872603945393041</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.027649932156912</v>
+        <v>1.956974423312637</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1404413469354033</v>
+        <v>0.1179788957479352</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.063251691192393</v>
+        <v>3.977159763232362</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.800094359936583</v>
+        <v>3.798310944616947</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.971139770275327</v>
+        <v>3.898525313027776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.767445032924009</v>
+        <v>-4.762597661915819</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.063805332791977</v>
+        <v>1.993129823947701</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1636459188526785</v>
+        <v>0.1411834676652104</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.069327321586934</v>
+        <v>3.983235393626902</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.787361500523298</v>
+        <v>3.785578085203662</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.975389780997301</v>
+        <v>3.90277532374975</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.747801673263141</v>
+        <v>-4.619538086174893</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.075912687378298</v>
+        <v>2.054603664966046</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1482918593283378</v>
+        <v>0.1491968942551897</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.064364896594304</v>
+        <v>3.992293460302864</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.779034987756564</v>
+        <v>3.777251572436928</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.982650663879838</v>
+        <v>3.910036206632286</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.446354947791304</v>
+        <v>-4.318091360703056</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.203752260449569</v>
+        <v>2.182443238037317</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.449738584800175</v>
+        <v>0.450643619727027</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.252493814759943</v>
+        <v>4.180422378468503</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.814433516384401</v>
+        <v>3.812650101064765</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.983621841632548</v>
+        <v>3.911007384384997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.501310144234373</v>
+        <v>-4.373046557146125</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.182741359625052</v>
+        <v>2.161432337212799</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.449738584800175</v>
+        <v>0.450643619727027</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.253464992512654</v>
+        <v>4.181393556221213</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.822981758178935</v>
+        <v>3.821198342859299</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.984464746012303</v>
+        <v>3.911850288764752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.450271768227853</v>
+        <v>-4.322008181139605</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.203999614407415</v>
+        <v>2.182690591995163</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.449738584800175</v>
+        <v>0.450643619727027</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.254307896892409</v>
+        <v>4.182236460600969</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.833532092674319</v>
+        <v>3.831748677354683</v>
       </c>
       <c r="C2032" t="n">
-        <v>4.003502844886449</v>
+        <v>3.930888387638898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.409132473361222</v>
+        <v>-4.280868886272974</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.239493431228213</v>
+        <v>2.218184408815961</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4908778796668058</v>
+        <v>0.4917829145936579</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.298029572686533</v>
+        <v>4.225958136395093</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.827550508405254</v>
+        <v>3.825767093085618</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.819686841010383</v>
+        <v>3.747072383762833</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.29852633328162</v>
+        <v>-4.170262746193372</v>
       </c>
       <c r="E2033" t="n">
-        <v>2.099919883383988</v>
+        <v>2.078610860971737</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6014840197464079</v>
+        <v>0.6023890546732599</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.180577252858228</v>
+        <v>4.108505816566789</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.806486536782416</v>
+        <v>3.80470312146278</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.823188885084347</v>
+        <v>3.750574427836797</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.429107067812462</v>
+        <v>-4.300843480724215</v>
       </c>
       <c r="E2034" t="n">
-        <v>2.051189633645615</v>
+        <v>2.029880611233363</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4709032852155653</v>
+        <v>0.4718083201424174</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.105730856213687</v>
+        <v>4.033659419922247</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.776826436538234</v>
+        <v>3.775043021218598</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.80761570416043</v>
+        <v>3.735001246912879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.264610733621501</v>
+        <v>-4.136347146533253</v>
       </c>
       <c r="E2035" t="n">
-        <v>2.101414986398082</v>
+        <v>2.08010596398583</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.4709032852155653</v>
+        <v>0.4718083201424174</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.090157675289769</v>
+        <v>4.01808623899833</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,45 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.823704766629952</v>
+        <v>3.821044820462776</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.806803414596859</v>
+        <v>3.734188957349309</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.140130252897549</v>
+        <v>-4.011866665809301</v>
       </c>
       <c r="E2036" t="n">
-        <v>2.150394889124092</v>
+        <v>2.129085866711841</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.4709032852155653</v>
+        <v>0.4718083201424174</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.089345385726199</v>
+        <v>4.01727394943476</v>
+      </c>
+    </row>
+    <row r="2037">
+      <c r="A2037" s="2" t="n">
+        <v>45499</v>
+      </c>
+      <c r="B2037" t="n">
+        <v>3.798063405827174</v>
+      </c>
+      <c r="C2037" t="n">
+        <v>3.838200357918308</v>
+      </c>
+      <c r="D2037" t="n">
+        <v>-4.011866665809301</v>
+      </c>
+      <c r="E2037" t="n">
+        <v>2.129085866711841</v>
+      </c>
+      <c r="F2037" t="n">
+        <v>0.4718083201424174</v>
+      </c>
+      <c r="G2037" t="n">
+        <v>3.831264154904676</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240726.xlsx
+++ b/tame_output/ON/bt/strategyON_20240726.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>21.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>84.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-28.1%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-76.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.4%</t>
+          <t>112.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.9%</t>
+          <t>125.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.3%</t>
+          <t>97.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.1%</t>
+          <t>-48.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.1%</t>
+          <t>-71.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>92.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>456.5%</t>
+          <t>452.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-562.8%</t>
+          <t>-573.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>99.2%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.2%</t>
+          <t>-37.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-45.6%</t>
+          <t>-44.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-163.3%</t>
+          <t>-159.2%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.3%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,27 +1293,27 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-263.7%</t>
+          <t>-267.4%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.4%</t>
+          <t>-27.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-91.2%</t>
+          <t>-168.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-176.8%</t>
+          <t>-179.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>78.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.5%</t>
+          <t>94.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-158.6%</t>
+          <t>-160.8%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.7%</t>
+          <t>-23.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>73.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-62.9%</t>
+          <t>-37.7%</t>
         </is>
       </c>
     </row>
@@ -43681,7 +43681,7 @@
         <v>45294</v>
       </c>
       <c r="B1832" t="n">
-        <v>3.301413393085798</v>
+        <v>3.301413393085799</v>
       </c>
       <c r="C1832" t="n">
         <v>3.130069279090508</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045691</v>
+        <v>3.317575502045692</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43785,10 +43785,10 @@
         <v>3.2775351796163</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.705385264837735</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.141232209668043</v>
+        <v>4.119052324986328</v>
       </c>
     </row>
     <row r="1837">
@@ -43808,10 +43808,10 @@
         <v>3.247868577088092</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.705385264837735</v>
+        <v>1.668418790368211</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.141721348393917</v>
+        <v>4.119541463712203</v>
       </c>
     </row>
     <row r="1838">
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511402</v>
+        <v>3.367379938511403</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43831,10 +43831,10 @@
         <v>3.197370603618793</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.568940374610322</v>
+        <v>1.531973900140798</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.063934396879136</v>
+        <v>4.041754512197421</v>
       </c>
     </row>
     <row r="1839">
@@ -43854,10 +43854,10 @@
         <v>3.137459091376417</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.568940374610322</v>
+        <v>1.531973900140798</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.098875481376678</v>
+        <v>4.076695596694964</v>
       </c>
     </row>
     <row r="1840">
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998558</v>
+        <v>3.367370539998559</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43877,10 +43877,10 @@
         <v>3.13805156785279</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.62458483087664</v>
+        <v>1.587618356407115</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.130839595321806</v>
+        <v>4.108659710640092</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082122</v>
+        <v>3.299560092082123</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43900,10 +43900,10 @@
         <v>3.013920335593304</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.367390796168583</v>
+        <v>1.330424321699059</v>
       </c>
       <c r="G1841" t="n">
-        <v>3.95526955612071</v>
+        <v>3.933089671438995</v>
       </c>
     </row>
     <row r="1842">
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.29349053375792</v>
+        <v>3.293490533757921</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43923,10 +43923,10 @@
         <v>2.988630988704009</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.367390796168583</v>
+        <v>1.330424321699059</v>
       </c>
       <c r="G1842" t="n">
-        <v>3.95628716525118</v>
+        <v>3.934107280569465</v>
       </c>
     </row>
     <row r="1843">
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760738</v>
+        <v>3.293766719760739</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43946,10 +43946,10 @@
         <v>2.897161149868867</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.367390796168583</v>
+        <v>1.330424321699059</v>
       </c>
       <c r="G1843" t="n">
-        <v>3.946915197238935</v>
+        <v>3.924735312557221</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706666</v>
+        <v>3.298730590706667</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43969,10 +43969,10 @@
         <v>2.854535115653005</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.394426369574719</v>
+        <v>1.357459895105195</v>
       </c>
       <c r="G1844" t="n">
-        <v>3.953219267237856</v>
+        <v>3.931039382556141</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296833</v>
+        <v>3.299918119296834</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -43992,10 +43992,10 @@
         <v>2.832416789337956</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.394426369574719</v>
+        <v>1.357459895105195</v>
       </c>
       <c r="G1845" t="n">
-        <v>3.957984584071558</v>
+        <v>3.935804699389843</v>
       </c>
     </row>
     <row r="1846">
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201484</v>
+        <v>3.295507330201485</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44015,10 +44015,10 @@
         <v>2.834797280119117</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.405815606229521</v>
+        <v>1.368849131759997</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.962642922183679</v>
+        <v>3.940463037501964</v>
       </c>
     </row>
     <row r="1847">
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153003</v>
+        <v>3.258791981153004</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44038,10 +44038,10 @@
         <v>2.665622562205445</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.9880615826826838</v>
+        <v>0.9510951082131597</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.70991739956064</v>
+        <v>3.687737514878926</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537423</v>
+        <v>3.271168579537424</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44061,10 +44061,10 @@
         <v>2.549436112162195</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.012143377422864</v>
+        <v>0.9751769029533396</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.72423269300367</v>
+        <v>3.702052808321955</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382188</v>
+        <v>3.272760131382189</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44084,10 +44084,10 @@
         <v>2.471126633374889</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.012143377422864</v>
+        <v>0.9751769029533396</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.729124837557595</v>
+        <v>3.70694495287588</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074619</v>
+        <v>3.25147557607462</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44107,10 +44107,10 @@
         <v>2.441336725248489</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.9499649662618935</v>
+        <v>0.9129984917923695</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.686899247199001</v>
+        <v>3.664719362517286</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911637</v>
+        <v>3.233800325911638</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44130,10 +44130,10 @@
         <v>2.287993533697077</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.5838962391172409</v>
+        <v>0.5469297646477168</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.460342310218659</v>
+        <v>3.438162425536944</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213493</v>
+        <v>3.223539378213494</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44153,10 +44153,10 @@
         <v>2.224935510855171</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.3754054576655564</v>
+        <v>0.3384389831960324</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.355586131086416</v>
+        <v>3.333406246404702</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416043</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44176,10 +44176,10 @@
         <v>2.134153787357651</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.3955588111643689</v>
+        <v>0.3585923366948448</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.375776893594272</v>
+        <v>3.353597008912558</v>
       </c>
     </row>
     <row r="1854">
@@ -44199,10 +44199,10 @@
         <v>1.938306168191745</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.09682621685972786</v>
+        <v>-0.1337926913292519</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.081452268823546</v>
+        <v>3.059272384141832</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495495</v>
+        <v>3.278199702495496</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44222,10 +44222,10 @@
         <v>1.782776550632579</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.09682621685972786</v>
+        <v>-0.1337926913292519</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.079994807636409</v>
+        <v>3.057814922954695</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347051</v>
+        <v>3.299136146347052</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44245,10 +44245,10 @@
         <v>1.684597402081363</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.06056349702926461</v>
+        <v>-0.09752997149878867</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.103521562989304</v>
+        <v>3.081341678307589</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130013</v>
+        <v>3.287377576130014</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44268,10 +44268,10 @@
         <v>1.598098749982812</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.2670752739162861</v>
+        <v>-0.3040417483858102</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.975720555513349</v>
+        <v>2.953540670831634</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178239</v>
+        <v>3.31588437417824</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44291,10 +44291,10 @@
         <v>1.472134046650871</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.2670752739162861</v>
+        <v>-0.3040417483858102</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.977493482213608</v>
+        <v>2.955313597531894</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207808</v>
+        <v>3.305316798207809</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44314,10 +44314,10 @@
         <v>1.28574461685836</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.4034927703575531</v>
+        <v>-0.4404592448270772</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.881975871816252</v>
+        <v>2.859795987134538</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310977</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44337,10 +44337,10 @@
         <v>1.18015179420743</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.3971565031282979</v>
+        <v>-0.434122977597822</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.874062407155896</v>
+        <v>2.851882522474182</v>
       </c>
     </row>
     <row r="1861">
@@ -44360,10 +44360,10 @@
         <v>1.044467326971214</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.4650874886172027</v>
+        <v>-0.5020539630867268</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.831884407518518</v>
+        <v>2.809704522836804</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309419</v>
+        <v>3.31108639130942</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44383,10 +44383,10 @@
         <v>1.020377155124307</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.3846419795235408</v>
+        <v>-0.4216084539930649</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.886639273208957</v>
+        <v>2.864459388527242</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.3047157169709</v>
+        <v>3.304715716970901</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44406,10 +44406,10 @@
         <v>0.8735807170746397</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.6809527638225534</v>
+        <v>-0.7179192382920774</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.708107317635381</v>
+        <v>2.685927432953667</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330518</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44429,10 +44429,10 @@
         <v>0.7089067502171269</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.126508015472756</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.461715595341733</v>
+        <v>2.439535710660019</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191732</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44452,10 +44452,10 @@
         <v>0.6585880178794419</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.126508015472756</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.456901027813193</v>
+        <v>2.434721143131479</v>
       </c>
     </row>
     <row r="1866">
@@ -44475,10 +44475,10 @@
         <v>0.4900253187735202</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.126508015472756</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.454895078422071</v>
+        <v>2.432715193740357</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097815</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44498,10 +44498,10 @@
         <v>0.4025754491513713</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.126508015472756</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.46515376909075</v>
+        <v>2.442973884409036</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309411</v>
+        <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44521,10 +44521,10 @@
         <v>0.2613716064398588</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.126508015472756</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.461253334236445</v>
+        <v>2.439073449554731</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119928</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44544,10 +44544,10 @@
         <v>0.2404953995979224</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.126508015472756</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.459658254291446</v>
+        <v>2.437478369609732</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969587</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44567,10 +44567,10 @@
         <v>0.1256098388030513</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.195251151206634</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.422191348780327</v>
+        <v>2.400011464098613</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923079</v>
+        <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44590,10 +44590,10 @@
         <v>0.04689565094492743</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.195251151206634</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.418165044245924</v>
+        <v>2.395985159564209</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297742</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44613,10 +44613,10 @@
         <v>-0.106407005873709</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.195251151206634</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.41806294292434</v>
+        <v>2.395883058242625</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131761</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44636,10 +44636,10 @@
         <v>-0.1056300679828341</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.162771121938499</v>
+        <v>-1.199737596408023</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.417942591774937</v>
+        <v>2.395762707093223</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737163</v>
+        <v>3.503515506737164</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44659,10 +44659,10 @@
         <v>-0.2440918936863845</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.162771121938499</v>
+        <v>-1.199737596408023</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.423292895072987</v>
+        <v>2.401113010391272</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341306</v>
+        <v>3.503170282341307</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44682,10 +44682,10 @@
         <v>-0.256315499110896</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.213120185392721</v>
+        <v>-1.250086659862245</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.400999476957631</v>
+        <v>2.378819592275917</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539457</v>
+        <v>3.501052558539458</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44705,10 +44705,10 @@
         <v>-0.2923214594576855</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.310739462814118</v>
+        <v>-1.347705937283642</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.345469661126562</v>
+        <v>2.323289776444848</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937496</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44728,10 +44728,10 @@
         <v>-0.311056502939457</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.364810962322477</v>
+        <v>-1.401777436792001</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.315920317743119</v>
+        <v>2.293740433061404</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141699</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.804813404801466</v>
+        <v>-8.818025609735649</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3819616939790871</v>
+        <v>-0.3872465759527599</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.514912358123934</v>
+        <v>-1.52941638140599</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.231372677380887</v>
+        <v>2.222670263411653</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729889</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.83846624330994</v>
+        <v>-8.851678448244122</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3909402748980404</v>
+        <v>-0.3962251568717132</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.615325726040971</v>
+        <v>-1.629829749323028</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.175607211115101</v>
+        <v>2.166904797145867</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.764996411642491</v>
+        <v>-9.023909650664432</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.3461806407376393</v>
+        <v>-0.449745936346416</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.541855894373523</v>
+        <v>-1.802060951743337</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.235060811608991</v>
+        <v>2.078937777187102</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.940120829029034</v>
+        <v>-9.199034068050976</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.4016751869447401</v>
+        <v>-0.5052404825535168</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.716980311760067</v>
+        <v>-1.977185369129881</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.144541381924581</v>
+        <v>1.988418347502693</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.174572923043524</v>
+        <v>-9.433486162065465</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.5026751894521317</v>
+        <v>-0.6062404850609084</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.716980311760067</v>
+        <v>-1.977185369129881</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.137322217022986</v>
+        <v>1.981199182601096</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.27894765406997</v>
+        <v>-9.537860893091912</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5510972726366865</v>
+        <v>-0.6546625682454632</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.821355042786512</v>
+        <v>-2.081560100156327</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.068025187633141</v>
+        <v>1.911902153211253</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.331733809670297</v>
+        <v>-9.590647048692238</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5710959450382611</v>
+        <v>-0.6746612406470378</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.91703052936891</v>
+        <v>-2.177235586738724</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.01173568552226</v>
+        <v>1.855612651100371</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297395</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.457770603038586</v>
+        <v>-9.716683842060528</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6188169337564622</v>
+        <v>-0.7223822293652389</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.891778906559167</v>
+        <v>-2.151983963928982</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.029580387837219</v>
+        <v>1.873457353415331</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.400698831142655</v>
+        <v>-9.659612070164597</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5919978893116888</v>
+        <v>-0.6955631849204655</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.891778906559167</v>
+        <v>-2.151983963928982</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.033570723523621</v>
+        <v>1.877447689101732</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.542370672866776</v>
+        <v>-9.801283911888717</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6501418529000786</v>
+        <v>-0.7537071485088553</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.891778906559167</v>
+        <v>-2.151983963928982</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.032095496624879</v>
+        <v>1.87597246220299</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.492779828441941</v>
+        <v>-9.751693067463883</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6152521049652728</v>
+        <v>-0.7188174005740495</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.842188062134333</v>
+        <v>-2.102393119504148</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.076903413444652</v>
+        <v>1.920780379022763</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.343861493970085</v>
+        <v>-9.602774732992026</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.568735904823213</v>
+        <v>-0.6723012004319897</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.81093847139916</v>
+        <v>-2.071143528768975</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.082602034239073</v>
+        <v>1.926478999817184</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.118016341250673</v>
+        <v>-9.376929580272616</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4688187706992397</v>
+        <v>-0.5723840663080169</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.769011795811997</v>
+        <v>-2.029216853181811</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.117337112627579</v>
+        <v>1.961214078205691</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.993437684913081</v>
+        <v>-9.252350923935024</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4178481636081441</v>
+        <v>-0.5214134592169213</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.769011795811997</v>
+        <v>-2.029216853181811</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.118476257183638</v>
+        <v>1.96235322276175</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.046332972957368</v>
+        <v>-9.305246211979311</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4363725046637512</v>
+        <v>-0.5399378002725284</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.76405644972355</v>
+        <v>-2.024261507093365</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.124083238998813</v>
+        <v>1.967960204576925</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.974199797669487</v>
+        <v>-9.23311303669143</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.401785530309962</v>
+        <v>-0.5053508259187396</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.76405644972355</v>
+        <v>-2.024261507093365</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.12981694323745</v>
+        <v>1.973693908815561</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.902833405059839</v>
+        <v>-9.161746644081783</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3829762356599682</v>
+        <v>-0.4865415312687458</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.692690057113903</v>
+        <v>-1.952895114483717</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.162899516409373</v>
+        <v>2.006776481987485</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.809374371074615</v>
+        <v>-9.068287610096558</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3554761033787863</v>
+        <v>-0.4590413989875635</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.692690057113903</v>
+        <v>-1.952895114483717</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.153016035096466</v>
+        <v>1.996893000674577</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.542132570206217</v>
+        <v>-8.80104580922816</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2504139435308006</v>
+        <v>-0.3539792391395782</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.692690057113903</v>
+        <v>-1.952895114483717</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.151181474597092</v>
+        <v>1.995058440175204</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.444225531529726</v>
+        <v>-8.70313877055167</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2115514430336654</v>
+        <v>-0.3151167386424425</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.624704307253346</v>
+        <v>-1.88490936462316</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.191672609539965</v>
+        <v>2.035549575118076</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.420271990553768</v>
+        <v>-8.679185229575712</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2013015204977884</v>
+        <v>-0.304866816106566</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.600750766277389</v>
+        <v>-1.860955823647203</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.206713240271033</v>
+        <v>2.050590205849145</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.156212052230972</v>
+        <v>-8.415125291252915</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1089378613304222</v>
+        <v>-0.2125031569391993</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.336690827954592</v>
+        <v>-1.596895885324407</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.351888887102959</v>
+        <v>2.19576585268107</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.449132428726133</v>
+        <v>-7.708045667748077</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1711069544112123</v>
+        <v>0.06754165880243512</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.336690827954592</v>
+        <v>-1.596895885324407</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.349101853442658</v>
+        <v>2.19297881902077</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.408948130359943</v>
+        <v>-7.667861369381886</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1875242976455298</v>
+        <v>0.08395900203675266</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.296506529588402</v>
+        <v>-1.556711586958216</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.373556056350214</v>
+        <v>2.217433021928326</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.24554825942058</v>
+        <v>-7.504461498442524</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2522510672420317</v>
+        <v>0.1486857716332546</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.133106658649039</v>
+        <v>-1.393311716018853</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.470962800134588</v>
+        <v>2.3148397657127</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.012067037190982</v>
+        <v>-7.270980276212925</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3535679849717237</v>
+        <v>0.2500026893629466</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8996254364194405</v>
+        <v>-1.159830493789255</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.6189759623102</v>
+        <v>2.462852927888311</v>
       </c>
     </row>
     <row r="1904">
@@ -45340,19 +45340,19 @@
         <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.083244556601354</v>
+        <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.862400646183467</v>
+        <v>-7.12131388520541</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3379278738142202</v>
+        <v>0.3069770354529933</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.8067219451769045</v>
+        <v>-1.066927002546719</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.599211389495212</v>
+        <v>2.515702812320874</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.078612043348381</v>
+        <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.73012517255258</v>
+        <v>-6.989038411574524</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3862055500136021</v>
+        <v>0.3552547116523748</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6744464715460179</v>
+        <v>-0.9346515289158321</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.673944160420771</v>
+        <v>2.590435583246433</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.081427104036018</v>
+        <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.574386839992838</v>
+        <v>-6.833300079014782</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4513159437251355</v>
+        <v>0.4203651053639081</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.5187081389862763</v>
+        <v>-0.7789131963560906</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.770202220644252</v>
+        <v>2.686693643469914</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.094333445259677</v>
+        <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.325387041309257</v>
+        <v>-6.584300280331201</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5638222044222267</v>
+        <v>0.5328713660609994</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.5187081389862763</v>
+        <v>-0.7789131963560906</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.783108561867911</v>
+        <v>2.699599984693573</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
-        <v>2.966357515660458</v>
+        <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.430977031082362</v>
+        <v>-6.689890270104305</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3936102789137657</v>
+        <v>0.3626594405525392</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.6242981287593807</v>
+        <v>-0.884503186129195</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.59177863840483</v>
+        <v>2.508270061230492</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987901</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.014901857537544</v>
+        <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.449711933200959</v>
+        <v>-6.708625172222902</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4346606599434133</v>
+        <v>0.4037098215821864</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.629894138419512</v>
+        <v>-0.8900991957893263</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.636965374485837</v>
+        <v>2.553456797311499</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.895022934849377</v>
+        <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.30177189179336</v>
+        <v>-6.560685130815303</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3739577538182854</v>
+        <v>0.3430069154570585</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.6095732225109545</v>
+        <v>-0.8697782798807687</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.529279001342804</v>
+        <v>2.445770424168466</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.886308948595898</v>
+        <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.248802369539371</v>
+        <v>-6.507715608561314</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3864315764664026</v>
+        <v>0.3554807381051761</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5566037002569656</v>
+        <v>-0.8168087576267798</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.552346728441719</v>
+        <v>2.468838151267382</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.879348336500805</v>
+        <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.205253962768681</v>
+        <v>-6.464167201790624</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3968903270795856</v>
+        <v>0.3659394887183591</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5566037002569656</v>
+        <v>-0.8168087576267798</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.545386116346626</v>
+        <v>2.461877539172288</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78292253349342</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.893810690881948</v>
+        <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.171890756289912</v>
+        <v>-6.430803995311855</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4246979640522364</v>
+        <v>0.3937471256910094</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5566037002569656</v>
+        <v>-0.8168087576267798</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.559848470727769</v>
+        <v>2.476339893553432</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.888342811341143</v>
+        <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.06363161916739</v>
+        <v>-6.322544858189334</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4625337393604401</v>
+        <v>0.4315829009992131</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5566037002569656</v>
+        <v>-0.8168087576267798</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.554380591186964</v>
+        <v>2.470872014012627</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.88584090535172</v>
+        <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.940340484350259</v>
+        <v>-6.199253723372203</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5093482872978692</v>
+        <v>0.4783974489366423</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.4333125654398351</v>
+        <v>-0.6935176228096493</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.625853366087819</v>
+        <v>2.542344788913482</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.893541883589045</v>
+        <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.919191285446816</v>
+        <v>-6.178104524468759</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5255089450965715</v>
+        <v>0.4945581067353451</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.4121633665363917</v>
+        <v>-0.672368423906206</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.646243863667211</v>
+        <v>2.562735286492873</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.889322591936096</v>
+        <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.675425843463372</v>
+        <v>-5.934339082485315</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.618795830237</v>
+        <v>0.5878449918757735</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.4121633665363917</v>
+        <v>-0.672368423906206</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.642024572014261</v>
+        <v>2.558515994839923</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824311233057524</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.891446905856112</v>
+        <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.573663023186077</v>
+        <v>-5.83257626220802</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6616252722679339</v>
+        <v>0.6306744339067074</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.398944298143963</v>
+        <v>-0.6591493555137773</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.652080326969735</v>
+        <v>2.568571749795397</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.884188980839814</v>
+        <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.323812629237002</v>
+        <v>-5.582725868258946</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.754307504831266</v>
+        <v>0.7233566664700395</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.398944298143963</v>
+        <v>-0.6591493555137773</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.644822401953437</v>
+        <v>2.561313824779099</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.887788104360463</v>
+        <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.14792053676957</v>
+        <v>-5.406833775791513</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8282634653388876</v>
+        <v>0.7973126269776611</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.398944298143963</v>
+        <v>-0.6591493555137773</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.648421525474085</v>
+        <v>2.564912948299748</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780933911392984</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.901115610415017</v>
+        <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.976474073747107</v>
+        <v>-5.23538731276905</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9101695566024266</v>
+        <v>0.8792187182412001</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.2274978351214999</v>
+        <v>-0.4877028924913142</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.764616909342117</v>
+        <v>2.681108332167779</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.900136088031314</v>
+        <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.902184508008768</v>
+        <v>-5.161097747030711</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9389058605140592</v>
+        <v>0.9079550221528327</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.1532082693831606</v>
+        <v>-0.4134133267529749</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.808211126401417</v>
+        <v>2.72470254922708</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.904830889085631</v>
+        <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.838548765774833</v>
+        <v>-5.097462004796776</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9690549584619503</v>
+        <v>0.9381041201007236</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.08957252714922609</v>
+        <v>-0.3497775845190403</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.851087372796095</v>
+        <v>2.767578795621758</v>
       </c>
     </row>
     <row r="1924">
@@ -45800,19 +45800,19 @@
         <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.886025147869427</v>
+        <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.727122006448913</v>
+        <v>-4.986035245470856</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9948199209761142</v>
+        <v>0.9638690826148875</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.08957252714922609</v>
+        <v>-0.3497775845190403</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.832281631579891</v>
+        <v>2.748773054405553</v>
       </c>
     </row>
     <row r="1925">
@@ -45823,19 +45823,19 @@
         <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.887768224494304</v>
+        <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.486691509644053</v>
+        <v>-4.745604748665996</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.092735196322935</v>
+        <v>1.061784357961709</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.1508579696556342</v>
+        <v>-0.1093470877141801</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.978283006287685</v>
+        <v>2.894774429113347</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.891697538329124</v>
+        <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.414448941472858</v>
+        <v>-4.673362180494801</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.125561537426234</v>
+        <v>1.094610699065007</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.1508579696556342</v>
+        <v>-0.1093470877141801</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.982212320122505</v>
+        <v>2.898703742948167</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.892376122246464</v>
+        <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.396735254594993</v>
+        <v>-4.655648493616936</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.13332559609472</v>
+        <v>1.102374757733493</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.154039298552551</v>
+        <v>-0.1061657588172633</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.984799701377995</v>
+        <v>2.901291124203657</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.889374193466458</v>
+        <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.287930369115266</v>
+        <v>-4.546843608137209</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.173845621506604</v>
+        <v>1.142894783145378</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.154039298552551</v>
+        <v>-0.1061657588172633</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.981797772597989</v>
+        <v>2.898289195423651</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.890953230477072</v>
+        <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.067909571078255</v>
+        <v>-4.326822810100198</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.263432977732022</v>
+        <v>1.232482139370796</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.2952591436205312</v>
+        <v>0.03505408625071699</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.068108716649391</v>
+        <v>2.984600139475053</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.906847413278895</v>
+        <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.935041882014977</v>
+        <v>-4.193955121036921</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.332474236159157</v>
+        <v>1.30152339779793</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.2952591436205312</v>
+        <v>0.03505408625071699</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.084002899451214</v>
+        <v>3.000494322276876</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.907993257719197</v>
+        <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.814868798650478</v>
+        <v>-4.073782037672422</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.381689313945258</v>
+        <v>1.350738475584031</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4154322269850302</v>
+        <v>0.1552271696152159</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.157252593910215</v>
+        <v>3.073744016735878</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.918081360280637</v>
+        <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.67019665355074</v>
+        <v>-3.929109892572685</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.449646274546593</v>
+        <v>1.418695436185366</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.5601043720847676</v>
+        <v>0.2998993147149533</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.254143983531498</v>
+        <v>3.17063540635716</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.904118851682063</v>
+        <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.730071480908433</v>
+        <v>-3.988984719930377</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.411733835004942</v>
+        <v>1.380782996643715</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5002295447270755</v>
+        <v>0.2400244873572612</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.204256578518308</v>
+        <v>3.12074800134397</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.919408020916271</v>
+        <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.610251249997595</v>
+        <v>-3.86916448901954</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.474951096603486</v>
+        <v>1.444000258242259</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5002295447270755</v>
+        <v>0.2400244873572612</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.219545747752517</v>
+        <v>3.136037170578179</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.827052220238713</v>
+        <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.612720956459401</v>
+        <v>-3.871634195481346</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.381607413341205</v>
+        <v>1.350656574979978</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.4977598382652693</v>
+        <v>0.2375547808954551</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.125708123197874</v>
+        <v>3.042199546023537</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.743220196003599</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.746314081724014</v>
+        <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.681091142783411</v>
+        <v>-3.940004381805355</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.273521200296902</v>
+        <v>1.242570361935675</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5070355373014842</v>
+        <v>0.24683047993167</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.050535404104905</v>
+        <v>2.967026826930567</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.736750790355905</v>
+        <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.694879195630458</v>
+        <v>-3.953792434652402</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.258442687789975</v>
+        <v>1.227491849428748</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5070355373014842</v>
+        <v>0.24683047993167</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.040972112736796</v>
+        <v>2.957463535562458</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.873781627048108</v>
+        <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.750399271523047</v>
+        <v>-4.009312510544992</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.373265494125142</v>
+        <v>1.342314655763915</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5070355373014842</v>
+        <v>0.24683047993167</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.178002949428999</v>
+        <v>3.094494372254661</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.878348859039896</v>
+        <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.574925011730578</v>
+        <v>-3.833838250752522</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.448022430033917</v>
+        <v>1.41707159167269</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5070355373014842</v>
+        <v>0.24683047993167</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.182570181420787</v>
+        <v>3.099061604246448</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.854090887801103</v>
+        <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.685861264371827</v>
+        <v>-3.944774503393771</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.379389957738625</v>
+        <v>1.348439119377398</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5070355373014842</v>
+        <v>0.24683047993167</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.158312210181994</v>
+        <v>3.074803633007655</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.782629201202552</v>
+        <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.652197718899545</v>
+        <v>-3.911110957921489</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.321393689328987</v>
+        <v>1.29044285096776</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5406990827737661</v>
+        <v>0.2804940254039519</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.107048650866812</v>
+        <v>3.023540073692474</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264163</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.792801587634685</v>
+        <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.592345099695822</v>
+        <v>-3.851258338717766</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.355507123442609</v>
+        <v>1.324556285081382</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5406990827737661</v>
+        <v>0.2804940254039519</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.117221037298945</v>
+        <v>3.033712460124607</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.787747858208545</v>
+        <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.506101636669444</v>
+        <v>-3.765014875691389</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.38495077922702</v>
+        <v>1.353999940865793</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5406990827737661</v>
+        <v>0.2804940254039519</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.112167307872805</v>
+        <v>3.028658730698467</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.779523633653071</v>
+        <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.551408456068424</v>
+        <v>-3.810321695090368</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.358603826911954</v>
+        <v>1.327652988550727</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.4998889197645353</v>
+        <v>0.2396838623947211</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.079456985511792</v>
+        <v>2.995948408337454</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.780075506686172</v>
+        <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.580441560770726</v>
+        <v>-3.83935479979267</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.347542458064135</v>
+        <v>1.316591619702908</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.4998889197645353</v>
+        <v>0.2396838623947211</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.080008858544894</v>
+        <v>2.996500281370556</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.709348198577538</v>
+        <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.487631079319867</v>
+        <v>-3.746544318341811</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.313939342535844</v>
+        <v>1.282988504174617</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.5926994012153947</v>
+        <v>0.3324943438455804</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.064967839306775</v>
+        <v>2.981459262132437</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.711221674502139</v>
+        <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.532020548649294</v>
+        <v>-3.790933787671238</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.298057030728674</v>
+        <v>1.267106192367447</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.548309931885967</v>
+        <v>0.2881048745161527</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.040207633633719</v>
+        <v>2.956699056459381</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.706297383013862</v>
+        <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.419349330413044</v>
+        <v>-3.678262569434988</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.338201226534897</v>
+        <v>1.30725038817367</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6609811501222171</v>
+        <v>0.4007760927524029</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.102886073087192</v>
+        <v>3.019377495912854</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.711788678844529</v>
+        <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.306972329230371</v>
+        <v>-3.565885568252316</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.388643322838633</v>
+        <v>1.357692484477406</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6609811501222171</v>
+        <v>0.4007760927524029</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.108377368917859</v>
+        <v>3.024868791743522</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.723285880613068</v>
+        <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.334752727131725</v>
+        <v>-3.593665966153669</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.389028365446631</v>
+        <v>1.358077527085404</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.633200752220864</v>
+        <v>0.3729956948510499</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.103206331945587</v>
+        <v>3.019697754771249</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.561641600613721</v>
+        <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.453133399861863</v>
+        <v>-3.712046638883807</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.180031816355229</v>
+        <v>1.149080977994002</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5659829000698878</v>
+        <v>0.3057778427000737</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.901231340655654</v>
+        <v>2.817722763481316</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.681791261332927</v>
+        <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.561747478305194</v>
+        <v>-3.820660717327138</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.256735845697102</v>
+        <v>1.225785007335875</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5659829000698878</v>
+        <v>0.3057778427000737</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.02138100137486</v>
+        <v>2.937872424200522</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.69630428743525</v>
+        <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.526338440057051</v>
+        <v>-3.785251679078995</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.285412487098682</v>
+        <v>1.254461648737455</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5659829000698878</v>
+        <v>0.3057778427000737</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.035894027477183</v>
+        <v>2.952385450302845</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.693723728777619</v>
+        <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.4879547774989</v>
+        <v>-3.746868016520844</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.298185393464311</v>
+        <v>1.267234555103084</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.604366562628039</v>
+        <v>0.3441615052582249</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.056343666354442</v>
+        <v>2.972835089180105</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.69045275762292</v>
+        <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.310838447463734</v>
+        <v>-3.569751686485678</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.365760954323679</v>
+        <v>1.334810115962453</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.604366562628039</v>
+        <v>0.3441615052582249</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.053072695199744</v>
+        <v>2.969564118025406</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.691136149384834</v>
+        <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.35593069229728</v>
+        <v>-3.614843931319224</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.348407448152174</v>
+        <v>1.317456609790947</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5424705194586492</v>
+        <v>0.2822654620888351</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.016618461060023</v>
+        <v>2.933109883885685</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.684923124691248</v>
+        <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.176555271058512</v>
+        <v>-3.435468510080456</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.413944591954096</v>
+        <v>1.382993753592869</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.6992472776293679</v>
+        <v>0.4390422202595538</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.104471491268869</v>
+        <v>3.020962914094531</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.665730580022838</v>
+        <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.221569484579118</v>
+        <v>-3.480482723601062</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.376746361877443</v>
+        <v>1.345795523516216</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6688983823147633</v>
+        <v>0.4086933249449491</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.067069609411696</v>
+        <v>2.983561032237358</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.671422142361783</v>
+        <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.488573994851554</v>
+        <v>-3.747487233873498</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.275636120107415</v>
+        <v>1.244685281746188</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4745353442718147</v>
+        <v>0.2143302869020006</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.956143348924873</v>
+        <v>2.872634771750535</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.670626064258285</v>
+        <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.589771776288726</v>
+        <v>-3.848685015310671</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.234360929429047</v>
+        <v>1.20341009106782</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4061265307264955</v>
+        <v>0.1459214733566814</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.914301982694183</v>
+        <v>2.830793405519845</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815456</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.668226025812602</v>
+        <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.583260809674414</v>
+        <v>-3.842174048696358</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.234565277629089</v>
+        <v>1.203614439267862</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4061265307264955</v>
+        <v>0.1459214733566814</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.911901944248499</v>
+        <v>2.828393367074161</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.664750745020847</v>
+        <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.564222681967117</v>
+        <v>-3.823135920989061</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.238705247920253</v>
+        <v>1.207754409559026</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.347942919395301</v>
+        <v>0.08773786202548683</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.873516496658028</v>
+        <v>2.79000791948369</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.842332613959527</v>
+        <v>2.914947071207078</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.595349313117735</v>
+        <v>-3.854262552139679</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.403836464398686</v>
+        <v>1.372885626037459</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.347942919395301</v>
+        <v>0.08773786202548683</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.051098365596708</v>
+        <v>2.96758978842237</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.843165942945661</v>
+        <v>2.915780400193211</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.609216074451652</v>
+        <v>-3.868129313473596</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.399123088851252</v>
+        <v>1.368172250490026</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.310085002661478</v>
+        <v>0.0498799452916639</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.029216944542548</v>
+        <v>2.94570836736821</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.849174473342587</v>
+        <v>2.921788930590137</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.564411902911722</v>
+        <v>-3.823325141933666</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.42305328786415</v>
+        <v>1.392102449502924</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.310085002661478</v>
+        <v>0.0498799452916639</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.035225474939474</v>
+        <v>2.951716897765136</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.747124694619786</v>
+        <v>2.819739151867337</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.41666893267672</v>
+        <v>-3.675582171698664</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.380100697235351</v>
+        <v>1.349149858874124</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4778923598963612</v>
+        <v>0.2176873025265471</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.033860110557603</v>
+        <v>2.950351533383265</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.749918316151267</v>
+        <v>2.822532773398818</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.518683615207941</v>
+        <v>-3.777596854229885</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.342088445754343</v>
+        <v>1.311137607393116</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4778923598963612</v>
+        <v>0.2176873025265471</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.036653732089084</v>
+        <v>2.953145154914746</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.750580664542925</v>
+        <v>2.823195121790476</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.512530909155156</v>
+        <v>-3.771444148177101</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.345211876567115</v>
+        <v>1.314261038205889</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4840450659491455</v>
+        <v>0.2238400085793313</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.041007704112413</v>
+        <v>2.957499126938075</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.749661141283036</v>
+        <v>2.822275598530586</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.529340207305658</v>
+        <v>-3.788253446327602</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.337568634047025</v>
+        <v>1.306617795685798</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4672357677986438</v>
+        <v>0.2070307104288297</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.030002601962222</v>
+        <v>2.946494024787885</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.815996695079857</v>
+        <v>2.888611152327407</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.467042208529536</v>
+        <v>-3.72595544755148</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.428823387354295</v>
+        <v>1.397872548993068</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4672357677986438</v>
+        <v>0.2070307104288297</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.096338155759043</v>
+        <v>3.012829578584705</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.618288696793984</v>
+        <v>2.690903154041534</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.265252010864378</v>
+        <v>-3.524165249886322</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.311831468134485</v>
+        <v>1.280880629773258</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6652539599677982</v>
+        <v>0.4050489025979841</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.017441072774663</v>
+        <v>2.933932495600325</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.688578929116159</v>
+        <v>2.761193386363709</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.316138723550573</v>
+        <v>-3.575051962572517</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.361767015382182</v>
+        <v>1.330816177020955</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.6143672472816037</v>
+        <v>0.3541621899117895</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.057199277485121</v>
+        <v>2.973690700310784</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.703206665232202</v>
+        <v>2.775821122479753</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.413879268175547</v>
+        <v>-3.672792507197491</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.337298533648236</v>
+        <v>1.306347695287009</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5984779691486235</v>
+        <v>0.3382729117788094</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.062293446721377</v>
+        <v>2.978784869547039</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.701742646056874</v>
+        <v>2.774357103304425</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.474088566180832</v>
+        <v>-3.733001805202776</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.311750795270794</v>
+        <v>1.280799956909567</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.538268671143339</v>
+        <v>0.2780636137735248</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.024703848742878</v>
+        <v>2.94119527156854</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397792</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.700234264096803</v>
+        <v>2.772848721344353</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.397666519748905</v>
+        <v>-3.656579758770849</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.340811231883493</v>
+        <v>1.309860393522266</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.538268671143339</v>
+        <v>0.2780636137735248</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.023195466782806</v>
+        <v>2.939686889608469</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.700097131532239</v>
+        <v>2.77271158877979</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.353293388110336</v>
+        <v>-3.61220662713228</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.358423351974357</v>
+        <v>1.32747251361313</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5826418027819076</v>
+        <v>0.3224367454120934</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.049682213201383</v>
+        <v>2.966173636027046</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105965</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.694490925670829</v>
+        <v>2.76710538291838</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.375773738969221</v>
+        <v>-3.634686977991165</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.343825005769394</v>
+        <v>1.312874167408167</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5826418027819076</v>
+        <v>0.3224367454120934</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.044076007339974</v>
+        <v>2.960567430165636</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190325</v>
+        <v>3.833011148190323</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.700872682698634</v>
+        <v>2.773487139946185</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.328118008408166</v>
+        <v>-3.58703124743011</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.36926905502162</v>
+        <v>1.338318216660394</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6302975333429632</v>
+        <v>0.3700924759731491</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.079051202704412</v>
+        <v>2.995542625530074</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.705765056073359</v>
+        <v>2.778379513320909</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.227599849909411</v>
+        <v>-3.486513088931355</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.414368691795847</v>
+        <v>1.38341785343462</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7308156918417178</v>
+        <v>0.4706106344719037</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.14425447117839</v>
+        <v>3.060745894004052</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557293</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.692519728549231</v>
+        <v>2.765134185796782</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.2882664403118</v>
+        <v>-3.547179679333744</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.376856728110764</v>
+        <v>1.345905889749537</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6491173751231841</v>
+        <v>0.38891231775337</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.081990153623142</v>
+        <v>2.998481576448804</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932768</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.69661743115986</v>
+        <v>2.76923188840741</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.243428038703402</v>
+        <v>-3.502341277725346</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.398889791364752</v>
+        <v>1.367938953003525</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6536608080680536</v>
+        <v>0.3934557506982395</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.088813916000692</v>
+        <v>3.005305338826354</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.700778370790938</v>
+        <v>2.773392828038488</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.26292649494541</v>
+        <v>-3.521839733967354</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.395251348499026</v>
+        <v>1.364300510137799</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6055761667881493</v>
+        <v>0.3453711094183352</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.064124070863827</v>
+        <v>2.98061549368949</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.706657973318775</v>
+        <v>2.779272430566325</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.21872365785951</v>
+        <v>-3.477636896881454</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.418812085861224</v>
+        <v>1.387861247499997</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6497790038740497</v>
+        <v>0.3895739465042356</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.096525375643205</v>
+        <v>3.013016798468867</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.705067973788022</v>
+        <v>2.777682431035573</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.255702685522953</v>
+        <v>-3.514615924544897</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.402430475265094</v>
+        <v>1.371479636903867</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6867529056653803</v>
+        <v>0.4265478482955661</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.117119717187251</v>
+        <v>3.033611140012913</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.756315738971062</v>
+        <v>2.828930196218613</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.097411267983681</v>
+        <v>-3.356324507005625</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.516994807463842</v>
+        <v>1.486043969102615</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6867529056653803</v>
+        <v>0.4265478482955661</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.16836748237029</v>
+        <v>3.084858905195953</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321021</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.754756443565315</v>
+        <v>2.827370900812866</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.889769264349205</v>
+        <v>-3.148682503371149</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.598492313511886</v>
+        <v>1.567541475150659</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8943949092998564</v>
+        <v>0.6341898519300423</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.291393389145229</v>
+        <v>3.207884811970891</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475138</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.749704671803585</v>
+        <v>2.822319129051136</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.838737171626676</v>
+        <v>-3.097650410648621</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.613853378839167</v>
+        <v>1.58290254047794</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9454270020223844</v>
+        <v>0.6852219446525702</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.316960873017016</v>
+        <v>3.233452295842678</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.76689207589629</v>
+        <v>2.839506533143841</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.773512990499471</v>
+        <v>-3.032426229521415</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.657130455382754</v>
+        <v>1.626179617021527</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.01065118314959</v>
+        <v>0.7504461257797759</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.373282785786044</v>
+        <v>3.289774208611707</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882557</v>
+        <v>3.840061186882555</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.76285304819557</v>
+        <v>2.835467505443121</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.736085970428337</v>
+        <v>-2.994999209450282</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.668062235710488</v>
+        <v>1.637111397349261</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.015902721178771</v>
+        <v>0.7556976638089575</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.372394680902834</v>
+        <v>3.288886103728496</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.764109840526811</v>
+        <v>2.836724297774361</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.756197626463046</v>
+        <v>-3.01511086548499</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.661274365627845</v>
+        <v>1.630323527266618</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.026930066176191</v>
+        <v>0.7667250088063767</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.380267880232525</v>
+        <v>3.296759303058188</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.924667611548021</v>
+        <v>2.997282068795572</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.702452812035841</v>
+        <v>-2.961366051057785</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.843330062419938</v>
+        <v>1.812379224058711</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.036993375616653</v>
+        <v>0.7767883182468387</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.546863636918014</v>
+        <v>3.463355059743676</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957624</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.044780520765839</v>
+        <v>3.117394978013389</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.627670551010828</v>
+        <v>-2.886583790032772</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.99335587604776</v>
+        <v>1.962405037686533</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.111775636641665</v>
+        <v>0.8515705792718513</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.711845902750838</v>
+        <v>3.628337325576501</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998755</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.036488496779698</v>
+        <v>3.109102954027248</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.60158646674702</v>
+        <v>-2.860499705768965</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.995497485767142</v>
+        <v>1.964546647405915</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.111775636641665</v>
+        <v>0.8515705792718513</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.703553878764697</v>
+        <v>3.62004530159036</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.034681692363477</v>
+        <v>3.107296149611028</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.523455285898073</v>
+        <v>-2.782368524920018</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.024943153690501</v>
+        <v>1.993992315329273</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.18595244752535</v>
+        <v>0.9257473901555359</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.746253160878688</v>
+        <v>3.66274458370435</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.052236098090269</v>
+        <v>3.124850555337819</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.51456282450479</v>
+        <v>-2.773476063526735</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.046054543974605</v>
+        <v>2.015103705613378</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.18595244752535</v>
+        <v>0.9257473901555359</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.763807566605479</v>
+        <v>3.680298989431141</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945363</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.044091145494852</v>
+        <v>3.116705602742403</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.683038941474668</v>
+        <v>-2.941952180496612</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.970519144591238</v>
+        <v>1.939568306230011</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.158004611808769</v>
+        <v>0.8977995544389551</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.738893912580114</v>
+        <v>3.655385335405776</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782705</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.025360842682714</v>
+        <v>3.097975299930265</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.985239412613085</v>
+        <v>-2.244152651635029</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.230908653323733</v>
+        <v>2.199957814962506</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.087656552438359</v>
+        <v>0.8274514950685443</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.677954774145729</v>
+        <v>3.594446196971392</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.016024865179619</v>
+        <v>3.08863932242717</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.962518308929933</v>
+        <v>-2.221431547951877</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.230661117293899</v>
+        <v>2.199710278932672</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.087656552438359</v>
+        <v>0.8274514950685443</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.668618796642634</v>
+        <v>3.585110219468296</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.78320569677767</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.174930991030788</v>
+        <v>3.247545448278339</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.091720122223975</v>
+        <v>-2.350633361245919</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.337886517827451</v>
+        <v>2.306935679466224</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9584547391443163</v>
+        <v>0.6982496817745021</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.750003834517378</v>
+        <v>3.66649525734304</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644409</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.212008813524434</v>
+        <v>3.284623270771985</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.246501129002231</v>
+        <v>-2.505414368024175</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.313051937609795</v>
+        <v>2.282101099248568</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9250870650898402</v>
+        <v>0.6648820077200259</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.767061052578339</v>
+        <v>3.683552475404001</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.20868416951398</v>
+        <v>3.28129862676153</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.239446438787057</v>
+        <v>-2.498359677809001</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.312549169685409</v>
+        <v>2.281598331324183</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.932141755305014</v>
+        <v>0.6719366979351997</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.767969222696988</v>
+        <v>3.684460645522651</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.218690323158721</v>
+        <v>3.291304780406272</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.212495214460569</v>
+        <v>-2.471408453482513</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.333335813060746</v>
+        <v>2.302384974699519</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.9470221013327331</v>
+        <v>0.6868170439629189</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.786903583958361</v>
+        <v>3.703395006784024</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.402793455303681</v>
+        <v>3.475407912551232</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.348448222516885</v>
+        <v>-2.607361461538829</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.46305774198318</v>
+        <v>2.432106903621952</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.9470221013327331</v>
+        <v>0.6868170439629189</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.971006716103321</v>
+        <v>3.887498138928983</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714424</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.394910150206674</v>
+        <v>3.467524607454225</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.370856340321757</v>
+        <v>-2.629769579343701</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.446211189764224</v>
+        <v>2.415260351402997</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.9470221013327331</v>
+        <v>0.6868170439629189</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.963123411006314</v>
+        <v>3.879614833831976</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.71911862715503</v>
+        <v>3.719118627155029</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.396964149756311</v>
+        <v>3.469578607003862</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.518862107801157</v>
+        <v>-2.823716118581438</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.389062882322102</v>
+        <v>2.339735735257539</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.8602950924691917</v>
+        <v>0.6314228375991542</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.913141205237826</v>
+        <v>3.848432309563355</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161975</v>
+        <v>3.729452285161974</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.453217867478159</v>
+        <v>3.525832324725709</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.528303033689687</v>
+        <v>-2.833157044469968</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.441540229688536</v>
+        <v>2.392213082623975</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.9827222100125831</v>
+        <v>0.7538499551425456</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.042851193485709</v>
+        <v>3.978142297811237</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321632</v>
+        <v>3.714941193321631</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.45610896202346</v>
+        <v>3.52872341927101</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.580576641025328</v>
+        <v>-2.885430651805609</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.423521881299581</v>
+        <v>2.374194734235019</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9304486026769418</v>
+        <v>0.7015763478069044</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.014378123629625</v>
+        <v>3.949669227955154</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.454220774917235</v>
+        <v>3.526835232164785</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.656906618626234</v>
+        <v>-2.961760629406515</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.391101703152994</v>
+        <v>2.341774556088432</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9304486026769418</v>
+        <v>0.7015763478069044</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.0124899365234</v>
+        <v>3.947781040848929</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.449041004520097</v>
+        <v>3.521655461767648</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.859160338950587</v>
+        <v>-3.164014349730869</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.305020444626115</v>
+        <v>2.255693297561553</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.7281948823525883</v>
+        <v>0.4993226274825509</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.88595793393165</v>
+        <v>3.821249038257179</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.447475014730249</v>
+        <v>3.5200894719778</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.020728764477842</v>
+        <v>-3.325582775258124</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.238827084625365</v>
+        <v>2.189499937560803</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.601411958554709</v>
+        <v>0.3725397036846715</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.808322189863075</v>
+        <v>3.743613294188603</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647104</v>
+        <v>3.754911907647102</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.460548421596168</v>
+        <v>3.533162878843719</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.153030056575396</v>
+        <v>-3.457884067355677</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.198979974652262</v>
+        <v>2.1496528275877</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.601411958554709</v>
+        <v>0.3725397036846715</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.821395596728994</v>
+        <v>3.756686701054522</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763531</v>
+        <v>3.74989685176353</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.460548421596168</v>
+        <v>3.533162878843719</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.154591699390256</v>
+        <v>-3.459445710170537</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.198355317526318</v>
+        <v>2.149028170461756</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.601411958554709</v>
+        <v>0.3725397036846715</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.821395596728994</v>
+        <v>3.756686701054522</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392115</v>
+        <v>3.715834055392113</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.45907246272317</v>
+        <v>3.531686919970721</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.182492486499729</v>
+        <v>-3.48734649728001</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.185719043809531</v>
+        <v>2.13639189674497</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5668150344117742</v>
+        <v>0.3379427795417367</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.799161483370235</v>
+        <v>3.734452587695763</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172526</v>
+        <v>3.684909939172525</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.455836906700369</v>
+        <v>3.528451363947919</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.305018589202623</v>
+        <v>-3.609872599982904</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.133473046705572</v>
+        <v>2.08414589964101</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4442889317088803</v>
+        <v>0.2154166768388428</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.722410265725697</v>
+        <v>3.657701370051226</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619362241971077</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.522542866290872</v>
+        <v>3.595157323538423</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.32507991047913</v>
+        <v>-3.629933921259411</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.192154477785473</v>
+        <v>2.142827330720912</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4242276104323733</v>
+        <v>0.1953553555623358</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.777079432550297</v>
+        <v>3.712370536875825</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199805</v>
+        <v>3.640764248199804</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.662854585292719</v>
+        <v>3.73546904254027</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.581800728473953</v>
+        <v>-3.886654739254235</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.229777869589391</v>
+        <v>2.180450722524829</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.3158130362885584</v>
+        <v>0.08694078141852096</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.852342407065855</v>
+        <v>3.787633511391383</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622235</v>
+        <v>3.668303164622234</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.731834854438359</v>
+        <v>3.80444931168591</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.735787146250094</v>
+        <v>-4.040641157030375</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.237163571624574</v>
+        <v>2.187836424560013</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.3158130362885584</v>
+        <v>0.08694078141852096</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.921322676211495</v>
+        <v>3.856613780537023</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808527</v>
+        <v>3.619937176808526</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.71788605655848</v>
+        <v>3.790500513806031</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.685265242422428</v>
+        <v>-3.990119253202709</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.243423535275761</v>
+        <v>2.1940963882112</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.3158130362885584</v>
+        <v>0.08694078141852096</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.907373878331616</v>
+        <v>3.842664982657144</v>
       </c>
     </row>
     <row r="2019">
@@ -47985,19 +47985,19 @@
         <v>3.656346893994892</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.729756545613894</v>
+        <v>3.802371002861445</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.937740396430153</v>
+        <v>-4.242594407210434</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.154303962728086</v>
+        <v>2.104976815663524</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.3158130362885584</v>
+        <v>0.08694078141852096</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.919244367387029</v>
+        <v>3.854535471712558</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358297</v>
+        <v>3.674042696358296</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.730967080132838</v>
+        <v>3.803581537380389</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.207213198351861</v>
+        <v>-4.512067209132142</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.047725376478346</v>
+        <v>1.998398229413785</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.3158130362885584</v>
+        <v>0.08694078141852096</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.920454901905973</v>
+        <v>3.855746006231501</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637085</v>
+        <v>3.663523617637084</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.735088822360159</v>
+        <v>3.80770327960771</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.364757270081302</v>
+        <v>-4.669611280861584</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.988829490013891</v>
+        <v>1.939502342949329</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.248911231148284</v>
+        <v>0.02003897627824647</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.88443556104913</v>
+        <v>3.819726665374658</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301342</v>
+        <v>3.652163313301341</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.730166675096349</v>
+        <v>3.802781132343899</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.642721665664576</v>
+        <v>-4.947575676444857</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.872721584516771</v>
+        <v>1.823394437452209</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.1592914968627997</v>
+        <v>-0.06958075800723779</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.825741573214029</v>
+        <v>3.761032677539557</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215468</v>
+        <v>3.667976467215467</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.892370731795393</v>
+        <v>3.964985189042944</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.759689358303467</v>
+        <v>-5.064543369083748</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.988138564160259</v>
+        <v>1.938811417095697</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.1592914968627997</v>
+        <v>-0.06958075800723779</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.987945629913073</v>
+        <v>3.923236734238601</v>
       </c>
     </row>
     <row r="2024">
@@ -48100,19 +48100,19 @@
         <v>3.69655362845669</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.887217369759207</v>
+        <v>3.959831827006758</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.84440730052442</v>
+        <v>-5.149261311304701</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.949098025235692</v>
+        <v>1.89977087817113</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.07417546793475333</v>
+        <v>-0.1546967869352842</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.931722650520059</v>
+        <v>3.867013754845587</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253286</v>
+        <v>3.750058176253285</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.897446787327698</v>
+        <v>3.970061244575249</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.926342118793303</v>
+        <v>-5.231196129573584</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.92655351549663</v>
+        <v>1.877226368432068</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.06424072234767314</v>
+        <v>-0.1646315325223643</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.935991220736303</v>
+        <v>3.871282325061831</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78364702771783</v>
+        <v>3.783647027717829</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.906372425783601</v>
+        <v>3.978986883031151</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.872603945393041</v>
+        <v>-5.177457956173322</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.956974423312637</v>
+        <v>1.907647276248075</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1179788957479352</v>
+        <v>-0.1108933591221022</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.977159763232362</v>
+        <v>3.91245086755789</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616947</v>
+        <v>3.798310944616946</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.898525313027776</v>
+        <v>3.971139770275327</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.762597661915819</v>
+        <v>-5.067451672696101</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.993129823947701</v>
+        <v>1.94380267688314</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1411834676652104</v>
+        <v>-0.08768878720482703</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.983235393626902</v>
+        <v>3.918526497952431</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203662</v>
+        <v>3.78557808520366</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.90277532374975</v>
+        <v>3.975389780997301</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.619538086174893</v>
+        <v>-4.924392096955176</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.054603664966046</v>
+        <v>2.005276517901484</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1491968942551897</v>
+        <v>-0.07967536061484776</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.992293460302864</v>
+        <v>3.927584564628393</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436928</v>
+        <v>3.777251572436927</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.910036206632286</v>
+        <v>3.982650663879838</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.318091360703056</v>
+        <v>-4.622945371483338</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.182443238037317</v>
+        <v>2.133116090972755</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.450643619727027</v>
+        <v>0.2217713648569895</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.180422378468503</v>
+        <v>4.115713482794032</v>
       </c>
     </row>
     <row r="2030">
@@ -48238,19 +48238,19 @@
         <v>3.812650101064765</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.911007384384997</v>
+        <v>3.983621841632548</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.373046557146125</v>
+        <v>-4.677900567926407</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.161432337212799</v>
+        <v>2.112105190148238</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.450643619727027</v>
+        <v>0.2217713648569895</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.181393556221213</v>
+        <v>4.116684660546742</v>
       </c>
     </row>
     <row r="2031">
@@ -48261,19 +48261,19 @@
         <v>3.821198342859299</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.911850288764752</v>
+        <v>3.984464746012303</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.322008181139605</v>
+        <v>-4.626862191919887</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.182690591995163</v>
+        <v>2.133363444930601</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.450643619727027</v>
+        <v>0.2217713648569895</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.182236460600969</v>
+        <v>4.117527564926498</v>
       </c>
     </row>
     <row r="2032">
@@ -48284,19 +48284,19 @@
         <v>3.831748677354683</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.930888387638898</v>
+        <v>4.003502844886449</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.280868886272974</v>
+        <v>-4.585722897053256</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.218184408815961</v>
+        <v>2.168857261751399</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4917829145936579</v>
+        <v>0.2629106597236203</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.225958136395093</v>
+        <v>4.161249240720621</v>
       </c>
     </row>
     <row r="2033">
@@ -48307,19 +48307,19 @@
         <v>3.825767093085618</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.747072383762833</v>
+        <v>3.819686841010383</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.170262746193372</v>
+        <v>-4.475116756973654</v>
       </c>
       <c r="E2033" t="n">
-        <v>2.078610860971737</v>
+        <v>2.029283713907175</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6023890546732599</v>
+        <v>0.3735167998032223</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.108505816566789</v>
+        <v>4.043796920892317</v>
       </c>
     </row>
     <row r="2034">
@@ -48330,19 +48330,19 @@
         <v>3.80470312146278</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.750574427836797</v>
+        <v>3.823188885084347</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.300843480724215</v>
+        <v>-4.605697491504497</v>
       </c>
       <c r="E2034" t="n">
-        <v>2.029880611233363</v>
+        <v>1.980553464168801</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4718083201424174</v>
+        <v>0.2429360652723798</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.033659419922247</v>
+        <v>3.968950524247775</v>
       </c>
     </row>
     <row r="2035">
@@ -48353,19 +48353,19 @@
         <v>3.775043021218598</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.735001246912879</v>
+        <v>3.80761570416043</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.136347146533253</v>
+        <v>-4.441201157313535</v>
       </c>
       <c r="E2035" t="n">
-        <v>2.08010596398583</v>
+        <v>2.030778816921268</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.4718083201424174</v>
+        <v>0.2429360652723798</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.01808623899833</v>
+        <v>3.953377343323858</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821044820462776</v>
+        <v>3.861658092494076</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.734188957349309</v>
+        <v>3.806803414596859</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.011866665809301</v>
+        <v>-4.316720676589584</v>
       </c>
       <c r="E2036" t="n">
-        <v>2.129085866711841</v>
+        <v>2.079758719647279</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.4718083201424174</v>
+        <v>0.2429360652723798</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.01727394943476</v>
+        <v>3.952565053760288</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.798063405827174</v>
+        <v>3.495407511871332</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.838200357918308</v>
+        <v>3.816672193721932</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.011866665809301</v>
+        <v>-4.114844409222481</v>
       </c>
       <c r="E2037" t="n">
-        <v>2.129085866711841</v>
+        <v>2.170378005719193</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4718083201424174</v>
+        <v>0.4448123326394832</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.831264154904676</v>
+        <v>4.083559593305622</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240726.xlsx
+++ b/tame_output/ON/bt/strategyON_20240726.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>23.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>82.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>64.0%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.1%</t>
+          <t>-77.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>112.0%</t>
+          <t>111.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>125.7%</t>
+          <t>125.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.3%</t>
+          <t>-46.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.9%</t>
+          <t>-73.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.8%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-573.1%</t>
+          <t>-610.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.2%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-37.0%</t>
+          <t>-34.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-44.5%</t>
+          <t>-47.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-159.2%</t>
+          <t>-180.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-22.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.3%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,27 +1293,27 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-267.4%</t>
+          <t>-263.7%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-10.7%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.5%</t>
+          <t>-26.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-168.1%</t>
+          <t>-114.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-179.5%</t>
+          <t>-221.2%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>94.5%</t>
+          <t>93.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-160.8%</t>
+          <t>-158.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.0%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-37.7%</t>
+          <t>-68.8%</t>
         </is>
       </c>
     </row>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355688</v>
+        <v>3.311888301355689</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43785,10 +43785,10 @@
         <v>3.2775351796163</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.668418790368211</v>
+        <v>1.705385264837735</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.119052324986328</v>
+        <v>4.141232209668043</v>
       </c>
     </row>
     <row r="1837">
@@ -43808,10 +43808,10 @@
         <v>3.247868577088092</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.668418790368211</v>
+        <v>1.705385264837735</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.119541463712203</v>
+        <v>4.141721348393917</v>
       </c>
     </row>
     <row r="1838">
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511403</v>
+        <v>3.367379938511402</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43831,10 +43831,10 @@
         <v>3.197370603618793</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.531973900140798</v>
+        <v>1.568940374610322</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.041754512197421</v>
+        <v>4.063934396879136</v>
       </c>
     </row>
     <row r="1839">
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386092</v>
+        <v>3.376932391386091</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43854,10 +43854,10 @@
         <v>3.137459091376417</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.531973900140798</v>
+        <v>1.568940374610322</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.076695596694964</v>
+        <v>4.098875481376678</v>
       </c>
     </row>
     <row r="1840">
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998559</v>
+        <v>3.367370539998558</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43877,10 +43877,10 @@
         <v>3.13805156785279</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.587618356407115</v>
+        <v>1.62458483087664</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.108659710640092</v>
+        <v>4.130839595321806</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082123</v>
+        <v>3.299560092082122</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43900,10 +43900,10 @@
         <v>3.013920335593304</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.330424321699059</v>
+        <v>1.367390796168583</v>
       </c>
       <c r="G1841" t="n">
-        <v>3.933089671438995</v>
+        <v>3.95526955612071</v>
       </c>
     </row>
     <row r="1842">
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757921</v>
+        <v>3.29349053375792</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43923,10 +43923,10 @@
         <v>2.988630988704009</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.330424321699059</v>
+        <v>1.367390796168583</v>
       </c>
       <c r="G1842" t="n">
-        <v>3.934107280569465</v>
+        <v>3.95628716525118</v>
       </c>
     </row>
     <row r="1843">
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760739</v>
+        <v>3.293766719760738</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43946,10 +43946,10 @@
         <v>2.897161149868867</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.330424321699059</v>
+        <v>1.367390796168583</v>
       </c>
       <c r="G1843" t="n">
-        <v>3.924735312557221</v>
+        <v>3.946915197238935</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706667</v>
+        <v>3.298730590706666</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43969,10 +43969,10 @@
         <v>2.854535115653005</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.357459895105195</v>
+        <v>1.394426369574719</v>
       </c>
       <c r="G1844" t="n">
-        <v>3.931039382556141</v>
+        <v>3.953219267237856</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296834</v>
+        <v>3.299918119296833</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -43992,10 +43992,10 @@
         <v>2.832416789337956</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.357459895105195</v>
+        <v>1.394426369574719</v>
       </c>
       <c r="G1845" t="n">
-        <v>3.935804699389843</v>
+        <v>3.957984584071558</v>
       </c>
     </row>
     <row r="1846">
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201485</v>
+        <v>3.295507330201484</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44015,10 +44015,10 @@
         <v>2.834797280119117</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.368849131759997</v>
+        <v>1.405815606229521</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.940463037501964</v>
+        <v>3.962642922183679</v>
       </c>
     </row>
     <row r="1847">
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153004</v>
+        <v>3.258791981153003</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44038,10 +44038,10 @@
         <v>2.665622562205445</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.9510951082131597</v>
+        <v>0.9880615826826838</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.687737514878926</v>
+        <v>3.70991739956064</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537424</v>
+        <v>3.271168579537423</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44061,10 +44061,10 @@
         <v>2.549436112162195</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.9751769029533396</v>
+        <v>1.012143377422864</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.702052808321955</v>
+        <v>3.72423269300367</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382189</v>
+        <v>3.272760131382188</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44084,10 +44084,10 @@
         <v>2.471126633374889</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.9751769029533396</v>
+        <v>1.012143377422864</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.70694495287588</v>
+        <v>3.729124837557595</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.25147557607462</v>
+        <v>3.251475576074619</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44107,10 +44107,10 @@
         <v>2.441336725248489</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.9129984917923695</v>
+        <v>0.9499649662618935</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.664719362517286</v>
+        <v>3.686899247199001</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911638</v>
+        <v>3.233800325911637</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44130,10 +44130,10 @@
         <v>2.287993533697077</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.5469297646477168</v>
+        <v>0.5838962391172409</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.438162425536944</v>
+        <v>3.460342310218659</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213494</v>
+        <v>3.223539378213493</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44153,10 +44153,10 @@
         <v>2.224935510855171</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.3384389831960324</v>
+        <v>0.3754054576655564</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.333406246404702</v>
+        <v>3.355586131086416</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416044</v>
+        <v>3.231167537416043</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44176,10 +44176,10 @@
         <v>2.134153787357651</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.3585923366948448</v>
+        <v>0.3955588111643689</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.353597008912558</v>
+        <v>3.375776893594272</v>
       </c>
     </row>
     <row r="1854">
@@ -44199,10 +44199,10 @@
         <v>1.938306168191745</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.1337926913292519</v>
+        <v>-0.09682621685972786</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.059272384141832</v>
+        <v>3.081452268823546</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495496</v>
+        <v>3.278199702495495</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44222,10 +44222,10 @@
         <v>1.782776550632579</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.1337926913292519</v>
+        <v>-0.09682621685972786</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.057814922954695</v>
+        <v>3.079994807636409</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347052</v>
+        <v>3.299136146347051</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44245,10 +44245,10 @@
         <v>1.684597402081363</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.09752997149878867</v>
+        <v>-0.06056349702926461</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.081341678307589</v>
+        <v>3.103521562989304</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130014</v>
+        <v>3.287377576130013</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44268,10 +44268,10 @@
         <v>1.598098749982812</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.3040417483858102</v>
+        <v>-0.2670752739162861</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.953540670831634</v>
+        <v>2.975720555513349</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.31588437417824</v>
+        <v>3.315884374178239</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44291,10 +44291,10 @@
         <v>1.472134046650871</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.3040417483858102</v>
+        <v>-0.2670752739162861</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.955313597531894</v>
+        <v>2.977493482213608</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207809</v>
+        <v>3.305316798207808</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44314,10 +44314,10 @@
         <v>1.28574461685836</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.4404592448270772</v>
+        <v>-0.4034927703575531</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.859795987134538</v>
+        <v>2.881975871816252</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310977</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44337,10 +44337,10 @@
         <v>1.18015179420743</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.434122977597822</v>
+        <v>-0.3971565031282979</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.851882522474182</v>
+        <v>2.874062407155896</v>
       </c>
     </row>
     <row r="1861">
@@ -44360,10 +44360,10 @@
         <v>1.044467326971214</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.5020539630867268</v>
+        <v>-0.4650874886172027</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.809704522836804</v>
+        <v>2.831884407518518</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130942</v>
+        <v>3.311086391309419</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44383,10 +44383,10 @@
         <v>1.020377155124307</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.4216084539930649</v>
+        <v>-0.3846419795235408</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.864459388527242</v>
+        <v>2.886639273208957</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.3047157169709</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44406,10 +44406,10 @@
         <v>0.8735807170746397</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.7179192382920774</v>
+        <v>-0.6809527638225534</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.685927432953667</v>
+        <v>2.708107317635381</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.300815818330518</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44429,10 +44429,10 @@
         <v>0.7089067502171269</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.126508015472756</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.439535710660019</v>
+        <v>2.461715595341733</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191732</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44452,10 +44452,10 @@
         <v>0.6585880178794419</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.126508015472756</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.434721143131479</v>
+        <v>2.456901027813193</v>
       </c>
     </row>
     <row r="1866">
@@ -44475,10 +44475,10 @@
         <v>0.4900253187735202</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.126508015472756</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.432715193740357</v>
+        <v>2.454895078422071</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097815</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44498,10 +44498,10 @@
         <v>0.4025754491513713</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.126508015472756</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.442973884409036</v>
+        <v>2.46515376909075</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094111</v>
+        <v>3.37443904309411</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44521,10 +44521,10 @@
         <v>0.2613716064398588</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.126508015472756</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.439073449554731</v>
+        <v>2.461253334236445</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.40596051119928</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44544,10 +44544,10 @@
         <v>0.2404953995979224</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.126508015472756</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.437478369609732</v>
+        <v>2.459658254291446</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969587</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44567,10 +44567,10 @@
         <v>0.1256098388030513</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.195251151206634</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.400011464098613</v>
+        <v>2.422191348780327</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923079</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44590,10 +44590,10 @@
         <v>0.04689565094492743</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.195251151206634</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.395985159564209</v>
+        <v>2.418165044245924</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297742</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44613,10 +44613,10 @@
         <v>-0.106407005873709</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.195251151206634</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.395883058242625</v>
+        <v>2.41806294292434</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.44775050131761</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44636,10 +44636,10 @@
         <v>-0.1056300679828341</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.199737596408023</v>
+        <v>-1.162771121938499</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.395762707093223</v>
+        <v>2.417942591774937</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737164</v>
+        <v>3.503515506737163</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44659,10 +44659,10 @@
         <v>-0.2440918936863845</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.199737596408023</v>
+        <v>-1.162771121938499</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.401113010391272</v>
+        <v>2.423292895072987</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341307</v>
+        <v>3.503170282341306</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44682,10 +44682,10 @@
         <v>-0.256315499110896</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.250086659862245</v>
+        <v>-1.213120185392721</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.378819592275917</v>
+        <v>2.400999476957631</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539458</v>
+        <v>3.501052558539457</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44705,10 +44705,10 @@
         <v>-0.2923214594576855</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.347705937283642</v>
+        <v>-1.310739462814118</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.323289776444848</v>
+        <v>2.345469661126562</v>
       </c>
     </row>
     <row r="1877">
@@ -44728,10 +44728,10 @@
         <v>-0.311056502939457</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.401777436792001</v>
+        <v>-1.364810962322477</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.293740433061404</v>
+        <v>2.315920317743119</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141699</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44751,10 +44751,10 @@
         <v>-0.3872465759527599</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.52941638140599</v>
+        <v>-1.492449906936466</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.222670263411653</v>
+        <v>2.244850148093368</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44774,10 +44774,10 @@
         <v>-0.3962251568717132</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.629829749323028</v>
+        <v>-1.592863274853503</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.166904797145867</v>
+        <v>2.189084681827581</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.023909650664432</v>
+        <v>-8.778208616576674</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.449745936346416</v>
+        <v>-0.3514655227113126</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.802060951743337</v>
+        <v>-1.519393443186055</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.078937777187102</v>
+        <v>2.248538282321471</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.199034068050976</v>
+        <v>-8.953333033963217</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.5052404825535168</v>
+        <v>-0.406960068918413</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.977185369129881</v>
+        <v>-1.694517860572599</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.988418347502693</v>
+        <v>2.158018852637062</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.433486162065465</v>
+        <v>-9.187785127977707</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.6062404850609084</v>
+        <v>-0.507960071425805</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.977185369129881</v>
+        <v>-1.694517860572599</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.981199182601096</v>
+        <v>2.150799687735466</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.537860893091912</v>
+        <v>-9.292159859004153</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.6546625682454632</v>
+        <v>-0.5563821546103598</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.081560100156327</v>
+        <v>-1.798892591599045</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.911902153211253</v>
+        <v>2.081502658345622</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.590647048692238</v>
+        <v>-9.34494601460448</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.6746612406470378</v>
+        <v>-0.5763808270119339</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.177235586738724</v>
+        <v>-1.894568078181442</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.855612651100371</v>
+        <v>2.025213156234741</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297395</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.716683842060528</v>
+        <v>-9.470982807972769</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.7223822293652389</v>
+        <v>-0.624101815730135</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.151983963928982</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.873457353415331</v>
+        <v>2.0430578585497</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.659612070164597</v>
+        <v>-9.413911036076838</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.6955631849204655</v>
+        <v>-0.5972827712853621</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.151983963928982</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.877447689101732</v>
+        <v>2.047048194236101</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.801283911888717</v>
+        <v>-9.555582877800958</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.7537071485088553</v>
+        <v>-0.6554267348737519</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.151983963928982</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.87597246220299</v>
+        <v>2.045572967337359</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.751693067463883</v>
+        <v>-9.505992033376124</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.7188174005740495</v>
+        <v>-0.6205369869389457</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.102393119504148</v>
+        <v>-1.819725610946866</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.920780379022763</v>
+        <v>2.090380884157132</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.602774732992026</v>
+        <v>-9.357073698904268</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.6723012004319897</v>
+        <v>-0.5740207867968863</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.071143528768975</v>
+        <v>-1.788476020211692</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.926478999817184</v>
+        <v>2.096079504951553</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.376929580272616</v>
+        <v>-9.131228546184857</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.5723840663080169</v>
+        <v>-0.4741036526729134</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.029216853181811</v>
+        <v>-1.746549344624529</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.961214078205691</v>
+        <v>2.13081458334006</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.252350923935024</v>
+        <v>-9.006649889847266</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.5214134592169213</v>
+        <v>-0.4231330455818179</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.029216853181811</v>
+        <v>-1.746549344624529</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.96235322276175</v>
+        <v>2.131953727896119</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.305246211979311</v>
+        <v>-9.059545177891552</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.5399378002725284</v>
+        <v>-0.4416573866374249</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.024261507093365</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.967960204576925</v>
+        <v>2.137560709711294</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.23311303669143</v>
+        <v>-8.987412002603671</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.5053508259187396</v>
+        <v>-0.4070704122836357</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.024261507093365</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.973693908815561</v>
+        <v>2.14329441394993</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.161746644081783</v>
+        <v>-8.916045609994024</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.4865415312687458</v>
+        <v>-0.3882611176336423</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.952895114483717</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.006776481987485</v>
+        <v>2.176376987121854</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.068287610096558</v>
+        <v>-8.822586576008799</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.4590413989875635</v>
+        <v>-0.36076098535246</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.952895114483717</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.996893000674577</v>
+        <v>2.166493505808947</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.80104580922816</v>
+        <v>-8.555344775140401</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3539792391395782</v>
+        <v>-0.2556988255044748</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.952895114483717</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.995058440175204</v>
+        <v>2.164658945309573</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.70313877055167</v>
+        <v>-8.457437736463911</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.3151167386424425</v>
+        <v>-0.2168363250073391</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.88490936462316</v>
+        <v>-1.602241856065878</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.035549575118076</v>
+        <v>2.205150080252446</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.679185229575712</v>
+        <v>-8.433484195487953</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.304866816106566</v>
+        <v>-0.2065864024714625</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.860955823647203</v>
+        <v>-1.578288315089921</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.050590205849145</v>
+        <v>2.220190710983514</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.415125291252915</v>
+        <v>-8.169424257165156</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.2125031569391993</v>
+        <v>-0.1142227433040959</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.596895885324407</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.19576585268107</v>
+        <v>2.365366357815439</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.708045667748077</v>
+        <v>-7.462344633660318</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.06754165880243512</v>
+        <v>0.1658220724375385</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.596895885324407</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.19297881902077</v>
+        <v>2.362579324155138</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.667861369381886</v>
+        <v>-7.422160335294127</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.08395900203675266</v>
+        <v>0.1822394156718561</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.556711586958216</v>
+        <v>-1.274044078400934</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.217433021928326</v>
+        <v>2.387033527062695</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.504461498442524</v>
+        <v>-7.258760464354765</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1486857716332546</v>
+        <v>0.246966185268358</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.393311716018853</v>
+        <v>-1.110644207461571</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.3148397657127</v>
+        <v>2.484440270847069</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.270980276212925</v>
+        <v>-7.025279242125166</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2500026893629466</v>
+        <v>0.34828310299805</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.159830493789255</v>
+        <v>-0.8771629852319727</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.462852927888311</v>
+        <v>2.632453433022681</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.12131388520541</v>
+        <v>-6.875612851117651</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3069770354529933</v>
+        <v>0.4052574490880967</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.066927002546719</v>
+        <v>-0.7842594939894367</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.515702812320874</v>
+        <v>2.685303317455243</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.989038411574524</v>
+        <v>-6.743337377486765</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3552547116523748</v>
+        <v>0.4535351252874782</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.9346515289158321</v>
+        <v>-0.6519840203585501</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.590435583246433</v>
+        <v>2.760036088380802</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.833300079014782</v>
+        <v>-6.701694488794898</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4203651053639081</v>
+        <v>0.4730073414518619</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.7789131963560906</v>
+        <v>-0.6103411316666831</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.686693643469914</v>
+        <v>2.787836882283559</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.584300280331201</v>
+        <v>-6.452694690111317</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5328713660609994</v>
+        <v>0.5855136021489531</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.7789131963560906</v>
+        <v>-0.6103411316666831</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.699599984693573</v>
+        <v>2.800743223507217</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.689890270104305</v>
+        <v>-6.558284679884421</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3626594405525392</v>
+        <v>0.4153016766404924</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.884503186129195</v>
+        <v>-0.7159311214397874</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.508270061230492</v>
+        <v>2.609413300044136</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.708625172222902</v>
+        <v>-6.577019582003018</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4037098215821864</v>
+        <v>0.4563520576701401</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.8900991957893263</v>
+        <v>-0.7215271310999187</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.553456797311499</v>
+        <v>2.654600036125144</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.560685130815303</v>
+        <v>-6.429079540595419</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3430069154570585</v>
+        <v>0.3956491515450122</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.8697782798807687</v>
+        <v>-0.7012062151913612</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.445770424168466</v>
+        <v>2.546913662982111</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.507715608561314</v>
+        <v>-6.37611001834143</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3554807381051761</v>
+        <v>0.4081229741931294</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.8168087576267798</v>
+        <v>-0.6482366929373723</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.468838151267382</v>
+        <v>2.569981390081026</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.464167201790624</v>
+        <v>-6.33256161157074</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3659394887183591</v>
+        <v>0.4185817248063124</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.8168087576267798</v>
+        <v>-0.6482366929373723</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.461877539172288</v>
+        <v>2.563020777985933</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.430803995311855</v>
+        <v>-6.299198405091971</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3937471256910094</v>
+        <v>0.4463893617789632</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.8168087576267798</v>
+        <v>-0.6482366929373723</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.476339893553432</v>
+        <v>2.577483132367076</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.322544858189334</v>
+        <v>-6.190939267969449</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4315829009992131</v>
+        <v>0.4842251370871669</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.8168087576267798</v>
+        <v>-0.6482366929373723</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.470872014012627</v>
+        <v>2.572015252826271</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.199253723372203</v>
+        <v>-6.067648133152319</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4783974489366423</v>
+        <v>0.531039685024596</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.6935176228096493</v>
+        <v>-0.5249455581202418</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.542344788913482</v>
+        <v>2.643488027727126</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.178104524468759</v>
+        <v>-6.046498934248875</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4945581067353451</v>
+        <v>0.5472003428232988</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.672368423906206</v>
+        <v>-0.5037963592167984</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.562735286492873</v>
+        <v>2.663878525306517</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.934339082485315</v>
+        <v>-5.802733492265431</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5878449918757735</v>
+        <v>0.6404872279637273</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.672368423906206</v>
+        <v>-0.5037963592167984</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.558515994839923</v>
+        <v>2.659659233653568</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.83257626220802</v>
+        <v>-5.700970671988136</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6306744339067074</v>
+        <v>0.6833166699946611</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.6591493555137773</v>
+        <v>-0.4905772908243697</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.568571749795397</v>
+        <v>2.669714988609041</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.582725868258946</v>
+        <v>-5.451120278039062</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7233566664700395</v>
+        <v>0.7759989025579932</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.6591493555137773</v>
+        <v>-0.4905772908243697</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.561313824779099</v>
+        <v>2.662457063592743</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.406833775791513</v>
+        <v>-5.275228185571629</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7973126269776611</v>
+        <v>0.8499548630656144</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.6591493555137773</v>
+        <v>-0.4905772908243697</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.564912948299748</v>
+        <v>2.666056187113392</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.23538731276905</v>
+        <v>-5.103781722549166</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8792187182412001</v>
+        <v>0.9318609543291538</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.4877028924913142</v>
+        <v>-0.3191308278019066</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.681108332167779</v>
+        <v>2.782251570981424</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.161097747030711</v>
+        <v>-5.029492156810827</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9079550221528327</v>
+        <v>0.9605972582407865</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.4134133267529749</v>
+        <v>-0.2448412620635673</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.72470254922708</v>
+        <v>2.825845788040724</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.097462004796776</v>
+        <v>-4.965856414576892</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9381041201007236</v>
+        <v>0.9907463561886773</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.3497775845190403</v>
+        <v>-0.1812055198296328</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.767578795621758</v>
+        <v>2.868722034435402</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.986035245470856</v>
+        <v>-4.854429655250972</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9638690826148875</v>
+        <v>1.016511318702841</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.3497775845190403</v>
+        <v>-0.1812055198296328</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.748773054405553</v>
+        <v>2.849916293219198</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.745604748665996</v>
+        <v>-4.613999158446112</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.061784357961709</v>
+        <v>1.114426594049662</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.1093470877141801</v>
+        <v>0.05922497697522749</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.894774429113347</v>
+        <v>2.995917667926991</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.673362180494801</v>
+        <v>-4.541756590274917</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.094610699065007</v>
+        <v>1.147252935152961</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.1093470877141801</v>
+        <v>0.05922497697522749</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.898703742948167</v>
+        <v>2.999846981761812</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.655648493616936</v>
+        <v>-4.524042903397052</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.102374757733493</v>
+        <v>1.155016993821447</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.1061657588172633</v>
+        <v>0.0624063058721443</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.901291124203657</v>
+        <v>3.002434363017302</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.546843608137209</v>
+        <v>-4.415238017917325</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.142894783145378</v>
+        <v>1.195537019233331</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.1061657588172633</v>
+        <v>0.0624063058721443</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.898289195423651</v>
+        <v>2.999432434237295</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.326822810100198</v>
+        <v>-4.195217219880314</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.232482139370796</v>
+        <v>1.285124375458749</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.03505408625071699</v>
+        <v>0.2036261509401245</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.984600139475053</v>
+        <v>3.085743378288698</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.193955121036921</v>
+        <v>-4.062349530817037</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.30152339779793</v>
+        <v>1.354165633885884</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.03505408625071699</v>
+        <v>0.2036261509401245</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.000494322276876</v>
+        <v>3.101637561090521</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.073782037672422</v>
+        <v>-3.942176447452538</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.350738475584031</v>
+        <v>1.403380711671985</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.1552271696152159</v>
+        <v>0.3237992343046235</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.073744016735878</v>
+        <v>3.174887255549522</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.929109892572685</v>
+        <v>-3.797504302352801</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.418695436185366</v>
+        <v>1.47133767227332</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.2998993147149533</v>
+        <v>0.4684713794043609</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.17063540635716</v>
+        <v>3.271778645170804</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.988984719930377</v>
+        <v>-3.857379129710493</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.380782996643715</v>
+        <v>1.433425232731669</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.2400244873572612</v>
+        <v>0.4085965520466688</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.12074800134397</v>
+        <v>3.221891240157615</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.86916448901954</v>
+        <v>-3.737558898799656</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.444000258242259</v>
+        <v>1.496642494330212</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.2400244873572612</v>
+        <v>0.4085965520466688</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.136037170578179</v>
+        <v>3.237180409391823</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.871634195481346</v>
+        <v>-3.740028605261462</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.350656574979978</v>
+        <v>1.403298811067931</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.2375547808954551</v>
+        <v>0.4061268455848626</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.042199546023537</v>
+        <v>3.143342784837181</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.940004381805355</v>
+        <v>-3.808398791585471</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.242570361935675</v>
+        <v>1.295212598023629</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.24683047993167</v>
+        <v>0.4154025446210776</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.967026826930567</v>
+        <v>3.068170065744212</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.953792434652402</v>
+        <v>-3.822186844432518</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.227491849428748</v>
+        <v>1.280134085516702</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.24683047993167</v>
+        <v>0.4154025446210776</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.957463535562458</v>
+        <v>3.058606774376103</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.946396084295658</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.009312510544992</v>
+        <v>-3.877706920325108</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.342314655763915</v>
+        <v>1.394956891851868</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.24683047993167</v>
+        <v>0.4154025446210776</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.094494372254661</v>
+        <v>3.195637611068305</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.950963316287446</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.833838250752522</v>
+        <v>-3.702232660532638</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.41707159167269</v>
+        <v>1.469713827760644</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.24683047993167</v>
+        <v>0.4154025446210776</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.099061604246448</v>
+        <v>3.200204843060093</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.926705345048653</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.944774503393771</v>
+        <v>-3.813168913173887</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.348439119377398</v>
+        <v>1.401081355465351</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.24683047993167</v>
+        <v>0.4154025446210776</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.074803633007655</v>
+        <v>3.1759468718213</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.855243658450103</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.911110957921489</v>
+        <v>-3.779505367701605</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.29044285096776</v>
+        <v>1.343085087055714</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.2804940254039519</v>
+        <v>0.4490660900933594</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.023540073692474</v>
+        <v>3.124683312506119</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.865416044882235</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.851258338717766</v>
+        <v>-3.719652748497882</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.324556285081382</v>
+        <v>1.377198521169335</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.2804940254039519</v>
+        <v>0.4490660900933594</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.033712460124607</v>
+        <v>3.134855698938251</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.860362315456096</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.765014875691389</v>
+        <v>-3.633409285471505</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.353999940865793</v>
+        <v>1.406642176953747</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.2804940254039519</v>
+        <v>0.4490660900933594</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.028658730698467</v>
+        <v>3.129801969512112</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.852138090900621</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.810321695090368</v>
+        <v>-3.678716104870484</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.327652988550727</v>
+        <v>1.38029522463868</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.2396838623947211</v>
+        <v>0.4082559270841286</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.995948408337454</v>
+        <v>3.097091647151099</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.852689963933723</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.83935479979267</v>
+        <v>-3.707749209572786</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.316591619702908</v>
+        <v>1.369233855790861</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.2396838623947211</v>
+        <v>0.4082559270841286</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.996500281370556</v>
+        <v>3.0976435201842</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.781962655825089</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.746544318341811</v>
+        <v>-3.800101986887902</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.282988504174617</v>
+        <v>1.26156543675618</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.3324943438455804</v>
+        <v>0.3159031497690124</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.981459262132437</v>
+        <v>2.971504545686496</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.783836131749689</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.790933787671238</v>
+        <v>-3.84449145621733</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.267106192367447</v>
+        <v>1.24568312494901</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.2881048745161527</v>
+        <v>0.2715136804395847</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.956699056459381</v>
+        <v>2.94674434001344</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.778911840261412</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.678262569434988</v>
+        <v>-3.73182023798108</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.30725038817367</v>
+        <v>1.285827320755233</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4007760927524029</v>
+        <v>0.3841848986758349</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.019377495912854</v>
+        <v>3.009422779466914</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.78440313609208</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.565885568252316</v>
+        <v>-3.619443236798407</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.357692484477406</v>
+        <v>1.33626941705897</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4007760927524029</v>
+        <v>0.3841848986758349</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.024868791743522</v>
+        <v>3.014914075297581</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.795900337860619</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.593665966153669</v>
+        <v>-3.64722363469976</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.358077527085404</v>
+        <v>1.336654459666967</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.3729956948510499</v>
+        <v>0.3564045007744819</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.019697754771249</v>
+        <v>3.009743038325308</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.634256057861272</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.712046638883807</v>
+        <v>-3.765604307429899</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.149080977994002</v>
+        <v>1.127657910575565</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3057778427000737</v>
+        <v>0.2891866486235057</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.817722763481316</v>
+        <v>2.807768047035375</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.754405718580478</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.820660717327138</v>
+        <v>-3.87421838587323</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.225785007335875</v>
+        <v>1.204361939917438</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3057778427000737</v>
+        <v>0.2891866486235057</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.937872424200522</v>
+        <v>2.927917707754581</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.768918744682801</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.785251679078995</v>
+        <v>-3.838809347625087</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.254461648737455</v>
+        <v>1.233038581319019</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3057778427000737</v>
+        <v>0.2891866486235057</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.952385450302845</v>
+        <v>2.942430733856904</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.766338186025169</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.746868016520844</v>
+        <v>-3.800425685066936</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.267234555103084</v>
+        <v>1.245811487684648</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.3441615052582249</v>
+        <v>0.3275703111816569</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.972835089180105</v>
+        <v>2.962880372734164</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.763067214870471</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.569751686485678</v>
+        <v>-3.62330935503177</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.334810115962453</v>
+        <v>1.313387048544016</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.3441615052582249</v>
+        <v>0.3275703111816569</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.969564118025406</v>
+        <v>2.959609401579466</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.763750606632384</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.614843931319224</v>
+        <v>-3.668401599865315</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.317456609790947</v>
+        <v>1.296033542372511</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.2822654620888351</v>
+        <v>0.2656742680122671</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.933109883885685</v>
+        <v>2.923155167439745</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.757537581938799</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.435468510080456</v>
+        <v>-3.489026178626547</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.382993753592869</v>
+        <v>1.361570686174432</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.4390422202595538</v>
+        <v>0.4224510261829857</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.020962914094531</v>
+        <v>3.01100819764859</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.738345037270388</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.480482723601062</v>
+        <v>-3.534040392147153</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.345795523516216</v>
+        <v>1.32437245609778</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4086933249449491</v>
+        <v>0.3921021308683811</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.983561032237358</v>
+        <v>2.973606315791417</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.744036599609334</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.747487233873498</v>
+        <v>-3.801044902419589</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.244685281746188</v>
+        <v>1.223262214327751</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.2143302869020006</v>
+        <v>0.1977390928254326</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.872634771750535</v>
+        <v>2.862680055304594</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.743240521505836</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.848685015310671</v>
+        <v>-3.902242683856762</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.20341009106782</v>
+        <v>1.181987023649384</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.1459214733566814</v>
+        <v>0.1293302792801134</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.830793405519845</v>
+        <v>2.820838689073904</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.740840483060152</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.842174048696358</v>
+        <v>-3.895731717242449</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.203614439267862</v>
+        <v>1.182191371849425</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.1459214733566814</v>
+        <v>0.1293302792801134</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.828393367074161</v>
+        <v>2.818438650628221</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.737365202268397</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.823135920989061</v>
+        <v>-3.876693589535152</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.207754409559026</v>
+        <v>1.186331342140589</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.08773786202548683</v>
+        <v>0.07114666794891883</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.79000791948369</v>
+        <v>2.780053203037749</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131249</v>
       </c>
       <c r="C1963" t="n">
         <v>2.914947071207078</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.854262552139679</v>
+        <v>-3.90782022068577</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.372885626037459</v>
+        <v>1.351462558619023</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.08773786202548683</v>
+        <v>0.07114666794891883</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.96758978842237</v>
+        <v>2.957635071976429</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.915780400193211</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.868129313473596</v>
+        <v>-3.921686982019687</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.368172250490026</v>
+        <v>1.346749183071589</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.0498799452916639</v>
+        <v>0.03328875121509589</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.94570836736821</v>
+        <v>2.935753650922269</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.921788930590137</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.823325141933666</v>
+        <v>-3.876882810479757</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.392102449502924</v>
+        <v>1.370679382084487</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.0498799452916639</v>
+        <v>0.03328875121509589</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.951716897765136</v>
+        <v>2.941762181319195</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.819739151867337</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.675582171698664</v>
+        <v>-3.729139840244755</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.349149858874124</v>
+        <v>1.327726791455687</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2176873025265471</v>
+        <v>0.201096108449979</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.950351533383265</v>
+        <v>2.940396816937324</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.822532773398818</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.777596854229885</v>
+        <v>-3.831154522775976</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.311137607393116</v>
+        <v>1.28971453997468</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2176873025265471</v>
+        <v>0.201096108449979</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.953145154914746</v>
+        <v>2.943190438468805</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.823195121790476</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.771444148177101</v>
+        <v>-3.825001816723192</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.314261038205889</v>
+        <v>1.292837970787452</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2238400085793313</v>
+        <v>0.2072488145027633</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.957499126938075</v>
+        <v>2.947544410492134</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.822275598530586</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.788253446327602</v>
+        <v>-3.841811114873693</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.306617795685798</v>
+        <v>1.285194728267362</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2070307104288297</v>
+        <v>0.1904395163522617</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.946494024787885</v>
+        <v>2.936539308341944</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.888611152327407</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.72595544755148</v>
+        <v>-3.779513116097571</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.397872548993068</v>
+        <v>1.376449481574631</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.2070307104288297</v>
+        <v>0.1904395163522617</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.012829578584705</v>
+        <v>3.002874862138765</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.690903154041534</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.524165249886322</v>
+        <v>-3.577722918432413</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.280880629773258</v>
+        <v>1.259457562354822</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.4050489025979841</v>
+        <v>0.3884577085214161</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.933932495600325</v>
+        <v>2.923977779154384</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.761193386363709</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.575051962572517</v>
+        <v>-3.628609631118608</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.330816177020955</v>
+        <v>1.309393109602519</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.3541621899117895</v>
+        <v>0.3375709958352215</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.973690700310784</v>
+        <v>2.963735983864843</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.775821122479753</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.672792507197491</v>
+        <v>-3.726350175743582</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.306347695287009</v>
+        <v>1.284924627868573</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.3382729117788094</v>
+        <v>0.3216817177022414</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.978784869547039</v>
+        <v>2.968830153101098</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.774357103304425</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.733001805202776</v>
+        <v>-3.786559473748867</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.280799956909567</v>
+        <v>1.259376889491131</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.2780636137735248</v>
+        <v>0.2614724196969568</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.94119527156854</v>
+        <v>2.931240555122599</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.772848721344353</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.656579758770849</v>
+        <v>-3.71013742731694</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.309860393522266</v>
+        <v>1.28843732610383</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.2780636137735248</v>
+        <v>0.2614724196969568</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.939686889608469</v>
+        <v>2.929732173162528</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.77271158877979</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.61220662713228</v>
+        <v>-3.665764295678371</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.32747251361313</v>
+        <v>1.306049446194694</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.3224367454120934</v>
+        <v>0.3058455513355254</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.966173636027046</v>
+        <v>2.956218919581105</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.76710538291838</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.634686977991165</v>
+        <v>-3.688244646537256</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.312874167408167</v>
+        <v>1.29145109998973</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.3224367454120934</v>
+        <v>0.3058455513355254</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.960567430165636</v>
+        <v>2.950612713719695</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.773487139946185</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.58703124743011</v>
+        <v>-3.640588915976201</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.338318216660394</v>
+        <v>1.316895149241957</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.3700924759731491</v>
+        <v>0.3535012818965811</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.995542625530074</v>
+        <v>2.985587909084134</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.778379513320909</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.486513088931355</v>
+        <v>-3.540070757477446</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.38341785343462</v>
+        <v>1.361994786016184</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.4706106344719037</v>
+        <v>0.4540194403953356</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.060745894004052</v>
+        <v>3.050791177558111</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.765134185796782</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.547179679333744</v>
+        <v>-3.600737347879835</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.345905889749537</v>
+        <v>1.3244828223311</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.38891231775337</v>
+        <v>0.372321123676802</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.998481576448804</v>
+        <v>2.988526860002863</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.76923188840741</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.502341277725346</v>
+        <v>-3.555898946271437</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.367938953003525</v>
+        <v>1.346515885585088</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.3934557506982395</v>
+        <v>0.3768645566216715</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.005305338826354</v>
+        <v>2.995350622380414</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.773392828038488</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.521839733967354</v>
+        <v>-3.575397402513445</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.364300510137799</v>
+        <v>1.342877442719363</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.3453711094183352</v>
+        <v>0.3287799153417671</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.98061549368949</v>
+        <v>2.970660777243549</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.779272430566325</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.477636896881454</v>
+        <v>-3.531194565427545</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.387861247499997</v>
+        <v>1.36643818008156</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.3895739465042356</v>
+        <v>0.3729827524276676</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.013016798468867</v>
+        <v>3.003062082022926</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.777682431035573</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.514615924544897</v>
+        <v>-3.568173593090988</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.371479636903867</v>
+        <v>1.350056569485431</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.4265478482955661</v>
+        <v>0.4099566542189981</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.033611140012913</v>
+        <v>3.023656423566972</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.828930196218613</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.356324507005625</v>
+        <v>-3.409882175551716</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.486043969102615</v>
+        <v>1.464620901684179</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.4265478482955661</v>
+        <v>0.4099566542189981</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.084858905195953</v>
+        <v>3.074904188750012</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.827370900812866</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.148682503371149</v>
+        <v>-3.20224017191724</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.567541475150659</v>
+        <v>1.546118407732223</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.6341898519300423</v>
+        <v>0.6175986578534742</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.207884811970891</v>
+        <v>3.197930095524951</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.822319129051136</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.097650410648621</v>
+        <v>-3.151208079194712</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.58290254047794</v>
+        <v>1.561479473059504</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.6852219446525702</v>
+        <v>0.6686307505760022</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.233452295842678</v>
+        <v>3.223497579396737</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.839506533143841</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.032426229521415</v>
+        <v>-3.085983898067506</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.626179617021527</v>
+        <v>1.604756549603091</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.7504461257797759</v>
+        <v>0.7338549317032078</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.289774208611707</v>
+        <v>3.279819492165766</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.835467505443121</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.994999209450282</v>
+        <v>-3.048556877996373</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.637111397349261</v>
+        <v>1.615688329930825</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.7556976638089575</v>
+        <v>0.7391064697323895</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.288886103728496</v>
+        <v>3.278931387282555</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.836724297774361</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.01511086548499</v>
+        <v>-3.068668534031081</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.630323527266618</v>
+        <v>1.608900459848182</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.7667250088063767</v>
+        <v>0.7501338147298087</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.296759303058188</v>
+        <v>3.286804586612247</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.997282068795572</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.961366051057785</v>
+        <v>-3.014923719603876</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.812379224058711</v>
+        <v>1.790956156640275</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.7767883182468387</v>
+        <v>0.7601971241702706</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.463355059743676</v>
+        <v>3.453400343297735</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.117394978013389</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.886583790032772</v>
+        <v>-2.940141458578863</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.962405037686533</v>
+        <v>1.940981970268097</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.8515705792718513</v>
+        <v>0.8349793851952833</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.628337325576501</v>
+        <v>3.61838260913056</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.109102954027248</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.860499705768965</v>
+        <v>-2.914057374315056</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.964546647405915</v>
+        <v>1.943123579987479</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.8515705792718513</v>
+        <v>0.8349793851952833</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.62004530159036</v>
+        <v>3.610090585144419</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896926</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
         <v>3.107296149611028</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.782368524920018</v>
+        <v>-2.835926193466109</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.993992315329273</v>
+        <v>1.972569247910837</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.9257473901555359</v>
+        <v>0.9091561960789678</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.66274458370435</v>
+        <v>3.652789867258409</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.124850555337819</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.773476063526735</v>
+        <v>-2.827033732072826</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.015103705613378</v>
+        <v>1.993680638194942</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.9257473901555359</v>
+        <v>0.9091561960789678</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.680298989431141</v>
+        <v>3.6703442729852</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945363</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
         <v>3.116705602742403</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.941952180496612</v>
+        <v>-2.995509849042703</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.939568306230011</v>
+        <v>1.918145238811575</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.8977995544389551</v>
+        <v>0.881208360362387</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.655385335405776</v>
+        <v>3.645430618959836</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782705</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>3.097975299930265</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.244152651635029</v>
+        <v>-2.29771032018112</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.199957814962506</v>
+        <v>2.17853474754407</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.8274514950685443</v>
+        <v>0.8108603009919764</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.594446196971392</v>
+        <v>3.584491480525451</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
         <v>3.08863932242717</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.221431547951877</v>
+        <v>-2.274989216497968</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.199710278932672</v>
+        <v>2.178287211514235</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.8274514950685443</v>
+        <v>0.8108603009919764</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.585110219468296</v>
+        <v>3.575155503022356</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.78320569677767</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
         <v>3.247545448278339</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.350633361245919</v>
+        <v>-2.40419102979201</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.306935679466224</v>
+        <v>2.285512612047787</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.6982496817745021</v>
+        <v>0.6816584876979341</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.66649525734304</v>
+        <v>3.656540540897099</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644409</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
         <v>3.284623270771985</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.505414368024175</v>
+        <v>-2.558972036570266</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.282101099248568</v>
+        <v>2.260678031830132</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.6648820077200259</v>
+        <v>0.648290813643458</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.683552475404001</v>
+        <v>3.67359775895806</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
         <v>3.28129862676153</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.498359677809001</v>
+        <v>-2.551917346355092</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.281598331324183</v>
+        <v>2.260175263905746</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.6719366979351997</v>
+        <v>0.6553455038586318</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.684460645522651</v>
+        <v>3.67450592907671</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
         <v>3.291304780406272</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.471408453482513</v>
+        <v>-2.524966122028604</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.302384974699519</v>
+        <v>2.280961907281083</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.6868170439629189</v>
+        <v>0.6702258498863509</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.703395006784024</v>
+        <v>3.693440290338083</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
         <v>3.475407912551232</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.607361461538829</v>
+        <v>-2.66091913008492</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.432106903621952</v>
+        <v>2.410683836203516</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.6868170439629189</v>
+        <v>0.6702258498863509</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.887498138928983</v>
+        <v>3.877543422483043</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
         <v>3.467524607454225</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.629769579343701</v>
+        <v>-2.683327247889792</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.415260351402997</v>
+        <v>2.393837283984561</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.6868170439629189</v>
+        <v>0.6702258498863509</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.879614833831976</v>
+        <v>3.869660117386036</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155029</v>
+        <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
         <v>3.469578607003862</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.823716118581438</v>
+        <v>-2.831333015369192</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.339735735257539</v>
+        <v>2.336688976542438</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.6314228375991542</v>
+        <v>0.5834988410228095</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.848432309563355</v>
+        <v>3.819677911617548</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161974</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
         <v>3.525832324725709</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.833157044469968</v>
+        <v>-3.01361946224789</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.392213082623975</v>
+        <v>2.320028115512806</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.7538499551425456</v>
+        <v>0.5338188111278889</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.978142297811237</v>
+        <v>3.846123611402443</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321631</v>
+        <v>3.714941193321633</v>
       </c>
       <c r="C2007" t="n">
         <v>3.52872341927101</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.885430651805609</v>
+        <v>-3.065893069583531</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.374194734235019</v>
+        <v>2.302009767123851</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.7015763478069044</v>
+        <v>0.4815452037922476</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.949669227955154</v>
+        <v>3.817650541546359</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.526835232164785</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.961760629406515</v>
+        <v>-3.142223047184437</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.341774556088432</v>
+        <v>2.269589588977263</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.7015763478069044</v>
+        <v>0.4815452037922476</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.947781040848929</v>
+        <v>3.815762354440134</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.521655461767648</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.164014349730869</v>
+        <v>-3.34447676750879</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.255693297561553</v>
+        <v>2.183508330450384</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.4993226274825509</v>
+        <v>0.2792914834678942</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.821249038257179</v>
+        <v>3.689230351848384</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
         <v>3.5200894719778</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.325582775258124</v>
+        <v>-3.506045193036045</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.189499937560803</v>
+        <v>2.117314970449635</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.3725397036846715</v>
+        <v>0.1525085596700148</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.743613294188603</v>
+        <v>3.611594607779809</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647102</v>
+        <v>3.754911907647104</v>
       </c>
       <c r="C2011" t="n">
         <v>3.533162878843719</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.457884067355677</v>
+        <v>-3.638346485133598</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.1496528275877</v>
+        <v>2.077467860476532</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.3725397036846715</v>
+        <v>0.1525085596700148</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.756686701054522</v>
+        <v>3.624668014645728</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74989685176353</v>
+        <v>3.749896851763532</v>
       </c>
       <c r="C2012" t="n">
         <v>3.533162878843719</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.459445710170537</v>
+        <v>-3.639908127948458</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.149028170461756</v>
+        <v>2.076843203350588</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.3725397036846715</v>
+        <v>0.1525085596700148</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.756686701054522</v>
+        <v>3.624668014645728</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392113</v>
+        <v>3.715834055392116</v>
       </c>
       <c r="C2013" t="n">
         <v>3.531686919970721</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.48734649728001</v>
+        <v>-3.667808915057931</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.13639189674497</v>
+        <v>2.064206929633801</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.3379427795417367</v>
+        <v>0.11791163552708</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.734452587695763</v>
+        <v>3.602433901286969</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172525</v>
+        <v>3.684909939172527</v>
       </c>
       <c r="C2014" t="n">
         <v>3.528451363947919</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.609872599982904</v>
+        <v>-3.790335017760825</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.08414589964101</v>
+        <v>2.011960932529842</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.2154166768388428</v>
+        <v>-0.004614467175813874</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.657701370051226</v>
+        <v>3.525682683642431</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971077</v>
+        <v>3.619362241971078</v>
       </c>
       <c r="C2015" t="n">
         <v>3.595157323538423</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.629933921259411</v>
+        <v>-3.810396339037332</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.142827330720912</v>
+        <v>2.070642363609743</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.1953553555623358</v>
+        <v>-0.02467578845232088</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.712370536875825</v>
+        <v>3.580351850467031</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199804</v>
+        <v>3.640764248199805</v>
       </c>
       <c r="C2016" t="n">
         <v>3.73546904254027</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.886654739254235</v>
+        <v>-4.067117157032156</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.180450722524829</v>
+        <v>2.108265755413661</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.08694078141852096</v>
+        <v>-0.1330903625961357</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.787633511391383</v>
+        <v>3.655614824982589</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622234</v>
+        <v>3.668303164622236</v>
       </c>
       <c r="C2017" t="n">
         <v>3.80444931168591</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.040641157030375</v>
+        <v>-4.221103574808296</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.187836424560013</v>
+        <v>2.115651457448844</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.08694078141852096</v>
+        <v>-0.1330903625961357</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.856613780537023</v>
+        <v>3.724595094128229</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808526</v>
+        <v>3.619937176808528</v>
       </c>
       <c r="C2018" t="n">
         <v>3.790500513806031</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.990119253202709</v>
+        <v>-4.17058167098063</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.1940963882112</v>
+        <v>2.121911421100031</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.08694078141852096</v>
+        <v>-0.1330903625961357</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.842664982657144</v>
+        <v>3.71064629624835</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994892</v>
+        <v>3.656346893994893</v>
       </c>
       <c r="C2019" t="n">
         <v>3.802371002861445</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.242594407210434</v>
+        <v>-4.423056824988355</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.104976815663524</v>
+        <v>2.032791848552356</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.08694078141852096</v>
+        <v>-0.1330903625961357</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.854535471712558</v>
+        <v>3.722516785303764</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358296</v>
+        <v>3.674042696358298</v>
       </c>
       <c r="C2020" t="n">
         <v>3.803581537380389</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.512067209132142</v>
+        <v>-4.692529626910063</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.998398229413785</v>
+        <v>1.926213262302616</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.08694078141852096</v>
+        <v>-0.1330903625961357</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.855746006231501</v>
+        <v>3.723727319822707</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637084</v>
+        <v>3.663523617637086</v>
       </c>
       <c r="C2021" t="n">
         <v>3.80770327960771</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.669611280861584</v>
+        <v>-4.850073698639505</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.939502342949329</v>
+        <v>1.867317375838161</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.02003897627824647</v>
+        <v>-0.1999921677364102</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.819726665374658</v>
+        <v>3.687707978965864</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301341</v>
+        <v>3.652163313301343</v>
       </c>
       <c r="C2022" t="n">
         <v>3.802781132343899</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.947575676444857</v>
+        <v>-5.128038094222778</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.823394437452209</v>
+        <v>1.751209470341041</v>
       </c>
       <c r="F2022" t="n">
-        <v>-0.06958075800723779</v>
+        <v>-0.2896119020218945</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.761032677539557</v>
+        <v>3.629013991130763</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215467</v>
+        <v>3.667976467215469</v>
       </c>
       <c r="C2023" t="n">
         <v>3.964985189042944</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.064543369083748</v>
+        <v>-5.245005786861669</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.938811417095697</v>
+        <v>1.866626449984528</v>
       </c>
       <c r="F2023" t="n">
-        <v>-0.06958075800723779</v>
+        <v>-0.2896119020218945</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.923236734238601</v>
+        <v>3.791218047829807</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.69655362845669</v>
+        <v>3.696553628456691</v>
       </c>
       <c r="C2024" t="n">
         <v>3.959831827006758</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.149261311304701</v>
+        <v>-5.329723729082622</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.89977087817113</v>
+        <v>1.827585911059961</v>
       </c>
       <c r="F2024" t="n">
-        <v>-0.1546967869352842</v>
+        <v>-0.3747279309499408</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.867013754845587</v>
+        <v>3.734995068436793</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253285</v>
+        <v>3.750058176253287</v>
       </c>
       <c r="C2025" t="n">
         <v>3.970061244575249</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.231196129573584</v>
+        <v>-5.411658547351506</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.877226368432068</v>
+        <v>1.8050414013209</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.1646315325223643</v>
+        <v>-0.384662676537021</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.871282325061831</v>
+        <v>3.739263638653037</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717829</v>
+        <v>3.783647027717831</v>
       </c>
       <c r="C2026" t="n">
         <v>3.978986883031151</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.177457956173322</v>
+        <v>-5.357920373951243</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.907647276248075</v>
+        <v>1.835462309136906</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.1108933591221022</v>
+        <v>-0.3309245031367589</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.91245086755789</v>
+        <v>3.780432181149096</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616946</v>
+        <v>3.798310944616948</v>
       </c>
       <c r="C2027" t="n">
         <v>3.971139770275327</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.067451672696101</v>
+        <v>-5.247914090474022</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.94380267688314</v>
+        <v>1.871617709771971</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.08768878720482703</v>
+        <v>-0.3077199312194837</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.918526497952431</v>
+        <v>3.786507811543637</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.78557808520366</v>
+        <v>3.785578085203663</v>
       </c>
       <c r="C2028" t="n">
         <v>3.975389780997301</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.924392096955176</v>
+        <v>-5.104854514733097</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.005276517901484</v>
+        <v>1.933091550790315</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.07967536061484776</v>
+        <v>-0.2997065046295044</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.927584564628393</v>
+        <v>3.795565878219599</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436927</v>
+        <v>3.777251572436929</v>
       </c>
       <c r="C2029" t="n">
         <v>3.982650663879838</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.622945371483338</v>
+        <v>-4.959012695854929</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.133116090972755</v>
+        <v>1.998689161224119</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.2217713648569895</v>
+        <v>-0.1538646857513367</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.115713482794032</v>
+        <v>3.890331852429036</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812650101064765</v>
+        <v>3.812650101064767</v>
       </c>
       <c r="C2030" t="n">
         <v>3.983621841632548</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.677900567926407</v>
+        <v>-5.013967892297998</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.112105190148238</v>
+        <v>1.977678260399601</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.2217713648569895</v>
+        <v>-0.1538646857513367</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.116684660546742</v>
+        <v>3.891303030181746</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821198342859299</v>
+        <v>3.821198342859301</v>
       </c>
       <c r="C2031" t="n">
         <v>3.984464746012303</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.626862191919887</v>
+        <v>-4.962929516291478</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.133363444930601</v>
+        <v>1.998936515181965</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.2217713648569895</v>
+        <v>-0.1538646857513367</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.117527564926498</v>
+        <v>3.892145934561502</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831748677354683</v>
+        <v>3.831748677354684</v>
       </c>
       <c r="C2032" t="n">
         <v>4.003502844886449</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.585722897053256</v>
+        <v>-4.921790221424847</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.168857261751399</v>
+        <v>2.034430332002763</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.2629106597236203</v>
+        <v>-0.1127253908847059</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.161249240720621</v>
+        <v>3.935867610355626</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825767093085618</v>
+        <v>3.82576709308562</v>
       </c>
       <c r="C2033" t="n">
         <v>3.819686841010383</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.475116756973654</v>
+        <v>-4.811184081345245</v>
       </c>
       <c r="E2033" t="n">
-        <v>2.029283713907175</v>
+        <v>1.894856784158538</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.3735167998032223</v>
+        <v>-0.002119250805103889</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.043796920892317</v>
+        <v>3.818415290527321</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.80470312146278</v>
+        <v>3.804703121462782</v>
       </c>
       <c r="C2034" t="n">
         <v>3.823188885084347</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.605697491504497</v>
+        <v>-4.941764815876088</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.980553464168801</v>
+        <v>1.846126534420165</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.2429360652723798</v>
+        <v>-0.1326999853359464</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.968950524247775</v>
+        <v>3.74356889388278</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775043021218598</v>
+        <v>3.775043021218599</v>
       </c>
       <c r="C2035" t="n">
         <v>3.80761570416043</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.441201157313535</v>
+        <v>-4.777268481685126</v>
       </c>
       <c r="E2035" t="n">
-        <v>2.030778816921268</v>
+        <v>1.896351887172632</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.2429360652723798</v>
+        <v>-0.1326999853359464</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.953377343323858</v>
+        <v>3.727995712958862</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.861658092494076</v>
+        <v>3.821044820462776</v>
       </c>
       <c r="C2036" t="n">
         <v>3.806803414596859</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.316720676589584</v>
+        <v>-4.652788000961174</v>
       </c>
       <c r="E2036" t="n">
-        <v>2.079758719647279</v>
+        <v>1.945331789898642</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.2429360652723798</v>
+        <v>-0.1326999853359464</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.952565053760288</v>
+        <v>3.727183423395292</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.495407511871332</v>
+        <v>3.516936947785943</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.816672193721932</v>
+        <v>3.756038479432809</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.114844409222481</v>
+        <v>-4.492557095350983</v>
       </c>
       <c r="E2037" t="n">
-        <v>2.170378005719193</v>
+        <v>1.958659216978668</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.4448123326394832</v>
+        <v>0.02753092027424553</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.083559593305622</v>
+        <v>3.772557031597356</v>
       </c>
     </row>
   </sheetData>
